--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,17 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3EEAF2-DBAE-4B09-BD51-4D55B51F4936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F72D92-86F7-4911-9C17-6A1169C31B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="2445" windowWidth="10335" windowHeight="8550" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="11" r:id="rId1"/>
+    <sheet name="總表" sheetId="11" r:id="rId1"/>
     <sheet name="搜尋詞對照" sheetId="14" r:id="rId2"/>
-    <sheet name="工作表2" sheetId="13" state="hidden" r:id="rId3"/>
+    <sheet name="內部公告" sheetId="15" r:id="rId3"/>
+    <sheet name="常用工具" sheetId="16" r:id="rId4"/>
+    <sheet name="工作表2" sheetId="13" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$B$1:$D$1776</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">總表!$B$1:$D$1776</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="555">
   <si>
     <t>序號</t>
   </si>
@@ -71,9 +73,6 @@
     <t>資料來源</t>
   </si>
   <si>
-    <t>關鍵字</t>
-  </si>
-  <si>
     <t>建立人</t>
   </si>
   <si>
@@ -104,18 +103,12 @@
     <t>ALNUS</t>
   </si>
   <si>
-    <t>&lt;4001376&gt;</t>
-  </si>
-  <si>
     <t>會晃是正常的嗎</t>
   </si>
   <si>
     <t>若商品為送達時會晃，請確認商品是否有長短腳情形，若商品為近日開始出現搖晃，請確認是否椅腳螺絲鬆馳重新擰緊，並確認椅腳是否皆貼地，若有搖晃情況可直接使用防滑墊墊高改善，或更換更換擺放位置讓四方桌腳均勻落地避免地形不平。</t>
   </si>
   <si>
-    <t>後台</t>
-  </si>
-  <si>
     <t>KB00002</t>
   </si>
   <si>
@@ -128,9 +121,6 @@
     <t xml:space="preserve">ALNUS </t>
   </si>
   <si>
-    <t>&lt;4001376&gt;&lt;4008061&gt;</t>
-  </si>
-  <si>
     <t>材質或外觀設計差異</t>
   </si>
   <si>
@@ -146,15 +136,9 @@
     <t>CERAL</t>
   </si>
   <si>
-    <t>&lt;4012560&gt;</t>
-  </si>
-  <si>
     <t>岩板底下的材質</t>
   </si>
   <si>
-    <t>關於您詢問的商品&lt;4012560&gt;◎岩板 陶板餐桌 CERAL X鐵腳款 150 GY/BK 岩板底下材質為中密度密集板。</t>
-  </si>
-  <si>
     <t>KB00004</t>
   </si>
   <si>
@@ -167,9 +151,6 @@
     <t>FILLN</t>
   </si>
   <si>
-    <t>&lt;4001099&gt;</t>
-  </si>
-  <si>
     <t>承重</t>
   </si>
   <si>
@@ -185,9 +166,6 @@
     <t>FILLN3</t>
   </si>
   <si>
-    <t>&lt;4010047&gt;</t>
-  </si>
-  <si>
     <t>重量</t>
   </si>
   <si>
@@ -215,9 +193,6 @@
     <t>HM201</t>
   </si>
   <si>
-    <t>&lt;4050268&gt;</t>
-  </si>
-  <si>
     <t>座面為獨立筒彈簧嗎</t>
   </si>
   <si>
@@ -231,9 +206,6 @@
   </si>
   <si>
     <t>IZZY2</t>
-  </si>
-  <si>
-    <t>&lt;4001437&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">餐椅耐重 </t>
@@ -263,9 +235,6 @@
     <t>JIGGY2</t>
   </si>
   <si>
-    <t>&lt;4010044&gt;</t>
-  </si>
-  <si>
     <t>材質</t>
   </si>
   <si>
@@ -284,12 +253,6 @@
     <t>LD2</t>
   </si>
   <si>
-    <t>&lt;2110100004438&gt;</t>
-  </si>
-  <si>
-    <t>買了這組沙發，但找不到USB供電用的電線插頭，請問是有遺漏配件嗎</t>
-  </si>
-  <si>
     <t>電源線插頭藏在底部白色裝飾布拉鏈處拉開即掉出，若是拉鍊拉開未找到零件，煩請您將拉鍊拉開並拍攝照片，寄至服務信箱：service@nitori.com.tw，標題為[售後 您的訂單編號]我們將以您的照片提出USB電源線零件申請，並使用快遞物流補寄給您。</t>
   </si>
   <si>
@@ -299,9 +262,6 @@
     <t>耐磨耐刮 防潑水貓抓布 布質左L型沙發 LD2 NSF MGY</t>
   </si>
   <si>
-    <t>&lt;2110100004445-4052088&gt;</t>
-  </si>
-  <si>
     <t>兩個沙發如何固定在一起</t>
   </si>
   <si>
@@ -315,9 +275,6 @@
   </si>
   <si>
     <t>N COLLECTION</t>
-  </si>
-  <si>
-    <t>&lt;2110100002410&gt;</t>
   </si>
   <si>
     <t>座面高</t>
@@ -1653,6 +1610,406 @@
   </si>
   <si>
     <t>尺寸規格</t>
+  </si>
+  <si>
+    <t>&lt;4001376&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>官網後台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林綉晏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林珈青</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>關鍵字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依商品搖晃發生時間、桌腳是否長短不一、螺絲是否鬆動及桌腳是否確實貼地判斷。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4001376&gt;&lt;4008061&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>羅中廷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>確認兩款商品的系列、桌腳造型、木材材質及搭配需求，並視需要建議至有展示品的門市比較。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4012560&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>岩板底下材質為中密度密集板。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>潘佳辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4001099&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4010047&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JOB MENU 商品庫存訊息--&gt; 商品資訊--&gt; 重量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JOB MENU 商品訊息搜尋--&gt; 管理尺寸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳宗霈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃暐翔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4050268&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4001437&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;4010044&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳怡蒨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;2110100004438&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>買了這組沙發，但找不到USB供電用的電線插頭，請問是有遺漏配件嗎</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;2110100004445-4052088&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;2110100002410&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>公告編號</t>
+  </si>
+  <si>
+    <t>公告標題</t>
+  </si>
+  <si>
+    <t>公告內容</t>
+  </si>
+  <si>
+    <t>公告日期</t>
+  </si>
+  <si>
+    <t>顯示狀態</t>
+  </si>
+  <si>
+    <t>活動日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>點數期限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【2026週年慶活動】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯示</t>
+  </si>
+  <si>
+    <t>顯示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 單筆消費實付金額滿500元，送 50點會員限期點數，滿1,000元送100點，以此類推，無上限。
+2. 指定家具最高現折 4,000 元（期間變價）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【2026 秋冬入會禮】</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/9/24～10/26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>限期點數: 2026/10/27 ～2026/12/13 
+一般點數: 消費日起 ~ 消費日隔年12/31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/9/24~12/28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>於期間內完成新會員註冊後立即贈送，贈送20點限期點數，點數匯入後即可使用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 限期點數: 加入會員起~2027/2/14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工具編號</t>
+  </si>
+  <si>
+    <t>工具名稱</t>
+  </si>
+  <si>
+    <t>工具說明</t>
+  </si>
+  <si>
+    <t>工具網址</t>
+  </si>
+  <si>
+    <t>顯示順序</t>
+  </si>
+  <si>
+    <t>工具分類</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顯示狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Teams</t>
+  </si>
+  <si>
+    <t>內部系統</t>
+  </si>
+  <si>
+    <t>客服信箱</t>
+  </si>
+  <si>
+    <t>PChome</t>
+  </si>
+  <si>
+    <t>網購訂單查詢</t>
+  </si>
+  <si>
+    <t>網購平台</t>
+  </si>
+  <si>
+    <t>MOMO</t>
+  </si>
+  <si>
+    <t>Rakuten</t>
+  </si>
+  <si>
+    <t>COMPANY</t>
+  </si>
+  <si>
+    <t>公司內部系統</t>
+  </si>
+  <si>
+    <t>官網後台</t>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>服務信箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/:x:/r/sites/Teams__NTW/_layouts/15/Doc.aspx?sourcedoc=%7B101395D8-2FB4-4E6A-A962-B8DCCFBAB1F9%7D&amp;file=%25u671d%25u79ae-%25u9867%25u5ba2%25u6d3d%25u8ac7%25u5ba4%25u66a8%25u547c%25u53eb%25u4e2d%25u5fc3.xlsx&amp;action=default&amp;mobileredirect=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洽談室朝禮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>洽談室班表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/:x:/r/sites/Teams_9636966253/_layouts/15/Doc.aspx?sourcedoc=%7BB230F05C-0764-4E6D-82B7-1411871B08FC%7D&amp;file=%E9%A1%A7%E5%AE%A2%E6%B4%BD%E8%AB%87%E5%AE%A4%E7%8F%AD%E8%A1%A82026.xlsx&amp;action=default&amp;mobileredirect=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitoribackendwin.azurewebsites.net/dashboard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rms.rakuten.com.tw/login#/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ecvdr.pchome.com.tw/v2016/login/v1/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://scm.momoshop.com.tw/manage/login.jsp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/:x:/r/sites/Teams_9636966253/_layouts/15/Doc.aspx?sourcedoc=%7BD3289924-A2E6-4386-96BD-9711A177B131%7D&amp;file=%E2%96%A0%20%E9%A1%A7%E5%AE%A2%E5%95%8F%E9%A1%8C%E5%BD%99%E6%95%B4%E8%A8%98%E9%8C%84%E8%A1%A8.xlsx&amp;action=default&amp;mobileredirect=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顧客問題彙整記錄表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>顧客問題回覆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日宣達</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大家ㄟ班表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>非電話紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B481ED728-B16B-4F2D-9179-BD79134E81B0%7D&amp;file=%E9%96%80%E5%B8%82%E8%87%AA%E5%8F%96%E5%88%B0%E8%B2%A8%E5%95%8F%E9%A1%8C%E5%9B%9E%E5%A0%B1.xlsx&amp;action=default&amp;mobileredirect=true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>門市自取用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>門市自取問題回報表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/:x:/s/Teams_-384/IQBOaMMnA7x1QZC6-4kKgLv-Af7TpbmlpptDofOrYKEIgxs?wdExp=TEAMS-TREATMENT&amp;web=1&amp;isSPOFile=1&amp;ovuser=94d67acc-8c17-4d3b-8463-9829cf08ef55%2Cchiaching_lin%40nitori.com.tw&amp;clickparams=eyJBcHBOYW1lIjoiVGVhbXMtRGVza3RvcCIsIkFwcFZlcnNpb24iOiI0OS8yNjA4MTMxOTMyMSIsIkhhc0ZlZGVyYXRlZFVzZXIiOmZhbHNlfQ%3D%3D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>網購售後用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>售後清單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B85DCED77-8281-4AD9-84EE-645E4378BB2D%7D&amp;file=%E7%9B%B4%E9%80%81%E6%89%98%E9%81%8B%E5%96%AE%E8%99%9F.xlsx&amp;action=default&amp;mobileredirect=true&amp;DefaultItemOpen=1&amp;ct=1735607179900&amp;wdOrigin=OFFICECOM-WEB.START.CONTENTACTIONS&amp;cid=ea813a7a-be11-41ac-b7e9-ee447bf0a5a2&amp;wdPreviousSessionSrc=HarmonyWeb&amp;wdPreviousSession=855bdce9-4bd9-49be-ae39-625e078be278</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直送托運單</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC直送查單號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ecmerchant.nccc.com.tw/ecmht/LoginMerchant.NCCC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NCCC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查官網信用卡交易紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.bpscm.com.tw/ASP/Login/Login.aspx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金財通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>發票寄出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://sms.mitake.com.tw/common/index.jsp?t=1790222541479</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>寄送簡訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三竹簡訊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://content.nitori-net.tw/nitorihome/common/imgcatch2.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多品抓圖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同時搜尋多樣商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://forms.cloud.microsoft/pages/responsepage.aspx?id=zHrWlBeMO02EY5gpzwjvVdSWENxQ1_VFnSafIvPS9t9UMEpRRklEVkpVSFBYUzdHUllMWEw5MkIwRiQlQCN0PWcu&amp;route=shorturl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配送意見回覆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配送中心或配送員客訴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://apsweb.hct.com.tw/SCTM/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新竹物流後台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查詢每日配送的紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1815,7 +2172,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1862,6 +2219,16 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -2162,15 +2529,16 @@
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="18" style="16" customWidth="1"/>
-    <col min="5" max="5" width="54.28515625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="18" style="16" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="54.28515625" style="16" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="26.5703125" customWidth="1"/>
     <col min="8" max="8" width="120.7109375" customWidth="1"/>
-    <col min="9" max="9" width="92.28515625" customWidth="1"/>
-    <col min="10" max="11" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="92.28515625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="47.140625" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2209,373 +2577,340 @@
         <v>10</v>
       </c>
       <c r="L1" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="M1" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>14</v>
-      </c>
-      <c r="P1" s="22" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="45">
       <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>25</v>
+      <c r="J2" s="23" t="s">
+        <v>455</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="N2" s="25">
-        <v>46287</v>
-      </c>
-      <c r="O2" s="3">
-        <v>7</v>
+        <v>45906.575694444444</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P2" s="25">
-        <v>46280</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="60">
       <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="22" t="s">
+      <c r="I3" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="J3" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="N3" s="25">
+        <v>45390.736111111109</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="P3" s="25">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="G4" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N3" s="25">
+      <c r="I4" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="N4" s="25">
+        <v>45083.507638888892</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="P4" s="25">
         <v>46288</v>
-      </c>
-      <c r="O3" s="3">
-        <v>7</v>
-      </c>
-      <c r="P3" s="25">
-        <v>46281</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="30">
-      <c r="A4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N4" s="25">
-        <v>46289</v>
-      </c>
-      <c r="O4" s="3">
-        <v>7</v>
-      </c>
-      <c r="P4" s="25">
-        <v>46282</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="45">
       <c r="A5" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>43</v>
+        <v>462</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="J5" s="3"/>
       <c r="K5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="N5" s="25">
-        <v>46290</v>
-      </c>
-      <c r="O5" s="3">
-        <v>7</v>
+        <v>45797.46597222222</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P5" s="25">
-        <v>46283</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="3" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>47</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>49</v>
+        <v>463</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>25</v>
+        <v>464</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="N6" s="25">
-        <v>46291</v>
-      </c>
-      <c r="O6" s="3">
-        <v>7</v>
+        <v>45810.418749999997</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P6" s="25">
-        <v>46284</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>55</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>25</v>
+        <v>465</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>466</v>
       </c>
       <c r="N7" s="25">
-        <v>46292</v>
-      </c>
-      <c r="O7" s="3">
-        <v>7</v>
+        <v>45708.677777777775</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P7" s="25">
-        <v>46285</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>59</v>
+        <v>468</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N8" s="25">
-        <v>46293</v>
-      </c>
-      <c r="O8" s="3">
-        <v>7</v>
+        <v>52</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P8" s="25">
         <v>46286</v>
@@ -2583,50 +2918,45 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>65</v>
+        <v>469</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M9" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="N9" s="25">
-        <v>46294</v>
-      </c>
-      <c r="O9" s="3">
-        <v>7</v>
+        <v>45717.698611111111</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P9" s="25">
         <v>46287</v>
@@ -2634,50 +2964,45 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>71</v>
+        <v>470</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3" t="s">
+        <v>471</v>
       </c>
       <c r="N10" s="25">
-        <v>46295</v>
-      </c>
-      <c r="O10" s="3">
-        <v>7</v>
+        <v>46184.647222222222</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P10" s="25">
         <v>46288</v>
@@ -2685,50 +3010,39 @@
     </row>
     <row r="11" spans="1:16" ht="45">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>78</v>
+        <v>472</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M11" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N11" s="25">
-        <v>46296</v>
-      </c>
-      <c r="O11" s="3">
-        <v>7</v>
+        <v>67</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P11" s="25">
         <v>46289</v>
@@ -2736,50 +3050,45 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>83</v>
+        <v>474</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>25</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="3">
-        <f>7</f>
-        <v>7</v>
+        <v>451</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>452</v>
       </c>
       <c r="N12" s="25">
-        <v>46297</v>
-      </c>
-      <c r="O12" s="3">
-        <v>7</v>
+        <v>45790.451388888891</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P12" s="25">
         <v>46290</v>
@@ -2787,50 +3096,41 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="3" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>89</v>
+        <v>475</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
       <c r="N13" s="25">
         <v>46298</v>
       </c>
-      <c r="O13" s="3">
-        <v>7</v>
+      <c r="O13" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P13" s="25">
         <v>46291</v>
@@ -2838,50 +3138,41 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
       <c r="N14" s="25">
         <v>46299</v>
       </c>
-      <c r="O14" s="3">
-        <v>7</v>
+      <c r="O14" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P14" s="25">
         <v>46292</v>
@@ -2889,50 +3180,41 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
       <c r="N15" s="25">
         <v>46300</v>
       </c>
-      <c r="O15" s="3">
-        <v>7</v>
+      <c r="O15" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P15" s="25">
         <v>46293</v>
@@ -2940,50 +3222,41 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M16" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
       <c r="N16" s="25">
         <v>46301</v>
       </c>
-      <c r="O16" s="3">
-        <v>7</v>
+      <c r="O16" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P16" s="25">
         <v>46294</v>
@@ -2991,50 +3264,41 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="3" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
       <c r="N17" s="25">
         <v>46302</v>
       </c>
-      <c r="O17" s="3">
-        <v>7</v>
+      <c r="O17" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P17" s="25">
         <v>46295</v>
@@ -3042,50 +3306,41 @@
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="3" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M18" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
       <c r="N18" s="25">
         <v>46303</v>
       </c>
-      <c r="O18" s="3">
-        <v>7</v>
+      <c r="O18" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P18" s="25">
         <v>46296</v>
@@ -3093,50 +3348,41 @@
     </row>
     <row r="19" spans="1:16" ht="30">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
       <c r="N19" s="25">
         <v>46304</v>
       </c>
-      <c r="O19" s="3">
-        <v>7</v>
+      <c r="O19" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P19" s="25">
         <v>46297</v>
@@ -3144,50 +3390,41 @@
     </row>
     <row r="20" spans="1:16" ht="30">
       <c r="A20" s="3" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M20" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
       <c r="N20" s="25">
         <v>46305</v>
       </c>
-      <c r="O20" s="3">
-        <v>7</v>
+      <c r="O20" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P20" s="25">
         <v>46298</v>
@@ -3195,50 +3432,41 @@
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="3" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M21" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
       <c r="N21" s="25">
         <v>46306</v>
       </c>
-      <c r="O21" s="3">
-        <v>7</v>
+      <c r="O21" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P21" s="25">
         <v>46299</v>
@@ -3246,50 +3474,41 @@
     </row>
     <row r="22" spans="1:16" ht="30">
       <c r="A22" s="3" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M22" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
       <c r="N22" s="25">
         <v>46307</v>
       </c>
-      <c r="O22" s="3">
-        <v>7</v>
+      <c r="O22" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P22" s="25">
         <v>46300</v>
@@ -3297,50 +3516,41 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M23" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
       <c r="N23" s="25">
         <v>46308</v>
       </c>
-      <c r="O23" s="3">
-        <v>7</v>
+      <c r="O23" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P23" s="25">
         <v>46301</v>
@@ -3348,50 +3558,41 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="3" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
       <c r="N24" s="25">
         <v>46309</v>
       </c>
-      <c r="O24" s="3">
-        <v>7</v>
+      <c r="O24" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P24" s="25">
         <v>46302</v>
@@ -3399,50 +3600,41 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M25" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
       <c r="N25" s="25">
         <v>46310</v>
       </c>
-      <c r="O25" s="3">
-        <v>7</v>
+      <c r="O25" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P25" s="25">
         <v>46303</v>
@@ -3450,50 +3642,41 @@
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="3" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
       <c r="N26" s="25">
         <v>46311</v>
       </c>
-      <c r="O26" s="3">
-        <v>7</v>
+      <c r="O26" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P26" s="25">
         <v>46304</v>
@@ -3501,50 +3684,41 @@
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" s="22" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
       <c r="N27" s="25">
         <v>46312</v>
       </c>
-      <c r="O27" s="3">
-        <v>7</v>
+      <c r="O27" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P27" s="25">
         <v>46305</v>
@@ -3552,50 +3726,41 @@
     </row>
     <row r="28" spans="1:16" ht="120">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" s="22" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
       <c r="N28" s="25">
         <v>46313</v>
       </c>
-      <c r="O28" s="3">
-        <v>7</v>
+      <c r="O28" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P28" s="25">
         <v>46306</v>
@@ -3603,50 +3768,41 @@
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29" s="22" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M29" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
       <c r="N29" s="25">
         <v>46314</v>
       </c>
-      <c r="O29" s="3">
-        <v>7</v>
+      <c r="O29" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P29" s="25">
         <v>46307</v>
@@ -3654,50 +3810,41 @@
     </row>
     <row r="30" spans="1:16">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E30" s="22" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
       <c r="N30" s="25">
         <v>46315</v>
       </c>
-      <c r="O30" s="3">
-        <v>7</v>
+      <c r="O30" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P30" s="25">
         <v>46308</v>
@@ -3705,50 +3852,41 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M31" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
       <c r="N31" s="25">
         <v>46316</v>
       </c>
-      <c r="O31" s="3">
-        <v>7</v>
+      <c r="O31" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P31" s="25">
         <v>46309</v>
@@ -3756,50 +3894,41 @@
     </row>
     <row r="32" spans="1:16" ht="45">
       <c r="A32" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M32" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
       <c r="N32" s="25">
         <v>46317</v>
       </c>
-      <c r="O32" s="3">
-        <v>7</v>
+      <c r="O32" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P32" s="25">
         <v>46310</v>
@@ -3807,50 +3936,41 @@
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M33" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
       <c r="N33" s="25">
         <v>46318</v>
       </c>
-      <c r="O33" s="3">
-        <v>7</v>
+      <c r="O33" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P33" s="25">
         <v>46311</v>
@@ -3858,50 +3978,41 @@
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="I34" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M34" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
       <c r="N34" s="25">
         <v>46319</v>
       </c>
-      <c r="O34" s="3">
-        <v>7</v>
+      <c r="O34" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P34" s="25">
         <v>46312</v>
@@ -3909,50 +4020,41 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
       <c r="N35" s="25">
         <v>46320</v>
       </c>
-      <c r="O35" s="3">
-        <v>7</v>
+      <c r="O35" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P35" s="25">
         <v>46313</v>
@@ -3960,50 +4062,41 @@
     </row>
     <row r="36" spans="1:16" ht="30">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
       <c r="N36" s="25">
         <v>46321</v>
       </c>
-      <c r="O36" s="3">
-        <v>7</v>
+      <c r="O36" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P36" s="25">
         <v>46314</v>
@@ -4011,50 +4104,41 @@
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="3" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E37" s="22" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M37" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
       <c r="N37" s="25">
         <v>46322</v>
       </c>
-      <c r="O37" s="3">
-        <v>7</v>
+      <c r="O37" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P37" s="25">
         <v>46315</v>
@@ -4062,50 +4146,41 @@
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M38" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
       <c r="N38" s="25">
         <v>46323</v>
       </c>
-      <c r="O38" s="3">
-        <v>7</v>
+      <c r="O38" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P38" s="25">
         <v>46316</v>
@@ -4113,50 +4188,41 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="3" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E39" s="22" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3"/>
       <c r="N39" s="25">
         <v>46324</v>
       </c>
-      <c r="O39" s="3">
-        <v>7</v>
+      <c r="O39" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P39" s="25">
         <v>46317</v>
@@ -4164,50 +4230,41 @@
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M40" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
       <c r="N40" s="25">
         <v>46325</v>
       </c>
-      <c r="O40" s="3">
-        <v>7</v>
+      <c r="O40" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P40" s="25">
         <v>46318</v>
@@ -4215,50 +4272,41 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="3" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M41" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
       <c r="N41" s="25">
         <v>46326</v>
       </c>
-      <c r="O41" s="3">
-        <v>7</v>
+      <c r="O41" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P41" s="25">
         <v>46319</v>
@@ -4266,50 +4314,41 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="I42" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M42" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
       <c r="N42" s="25">
         <v>46327</v>
       </c>
-      <c r="O42" s="3">
-        <v>7</v>
+      <c r="O42" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P42" s="25">
         <v>46320</v>
@@ -4317,50 +4356,41 @@
     </row>
     <row r="43" spans="1:16" ht="30">
       <c r="A43" s="3" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E43" s="22" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M43" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="J43" s="3"/>
+      <c r="K43" s="3"/>
+      <c r="L43" s="3"/>
+      <c r="M43" s="3"/>
       <c r="N43" s="25">
         <v>46328</v>
       </c>
-      <c r="O43" s="3">
-        <v>7</v>
+      <c r="O43" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P43" s="25">
         <v>46321</v>
@@ -4368,50 +4398,41 @@
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="3" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" s="22" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M44" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
+      <c r="M44" s="3"/>
       <c r="N44" s="25">
         <v>46329</v>
       </c>
-      <c r="O44" s="3">
-        <v>7</v>
+      <c r="O44" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P44" s="25">
         <v>46322</v>
@@ -4419,50 +4440,41 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="3" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" s="22" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="F45" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I45" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I45" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M45" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
+      <c r="M45" s="3"/>
       <c r="N45" s="25">
         <v>46330</v>
       </c>
-      <c r="O45" s="3">
-        <v>7</v>
+      <c r="O45" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P45" s="25">
         <v>46323</v>
@@ -4470,50 +4482,41 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="3" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M46" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
+      <c r="M46" s="3"/>
       <c r="N46" s="25">
         <v>46331</v>
       </c>
-      <c r="O46" s="3">
-        <v>7</v>
+      <c r="O46" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P46" s="25">
         <v>46324</v>
@@ -4521,50 +4524,41 @@
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="3" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M47" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
+      <c r="M47" s="3"/>
       <c r="N47" s="25">
         <v>46332</v>
       </c>
-      <c r="O47" s="3">
-        <v>7</v>
+      <c r="O47" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P47" s="25">
         <v>46325</v>
@@ -4572,50 +4566,41 @@
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="3" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E48" s="22" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
       <c r="N48" s="25">
         <v>46333</v>
       </c>
-      <c r="O48" s="3">
-        <v>7</v>
+      <c r="O48" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P48" s="25">
         <v>46326</v>
@@ -4623,50 +4608,41 @@
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="3" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E49" s="22" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I49" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
       <c r="N49" s="25">
         <v>46334</v>
       </c>
-      <c r="O49" s="3">
-        <v>7</v>
+      <c r="O49" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P49" s="25">
         <v>46327</v>
@@ -4674,50 +4650,41 @@
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E50" s="22" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
       <c r="N50" s="25">
         <v>46335</v>
       </c>
-      <c r="O50" s="3">
-        <v>7</v>
+      <c r="O50" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P50" s="25">
         <v>46328</v>
@@ -4725,50 +4692,41 @@
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="3" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E51" s="22" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I51" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M51" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
       <c r="N51" s="25">
         <v>46336</v>
       </c>
-      <c r="O51" s="3">
-        <v>7</v>
+      <c r="O51" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P51" s="25">
         <v>46329</v>
@@ -4776,50 +4734,41 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="I52" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M52" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
       <c r="N52" s="25">
         <v>46337</v>
       </c>
-      <c r="O52" s="3">
-        <v>7</v>
+      <c r="O52" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P52" s="25">
         <v>46330</v>
@@ -4827,50 +4776,41 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="3" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M53" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
+      <c r="M53" s="3"/>
       <c r="N53" s="25">
         <v>46338</v>
       </c>
-      <c r="O53" s="3">
-        <v>7</v>
+      <c r="O53" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P53" s="25">
         <v>46331</v>
@@ -4878,50 +4818,41 @@
     </row>
     <row r="54" spans="1:16">
       <c r="A54" s="3" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="I54" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M54" s="3">
-        <f>7</f>
-        <v>7</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="J54" s="3"/>
+      <c r="K54" s="3"/>
+      <c r="L54" s="3"/>
+      <c r="M54" s="3"/>
       <c r="N54" s="25">
         <v>46339</v>
       </c>
-      <c r="O54" s="3">
-        <v>7</v>
+      <c r="O54" s="3" t="s">
+        <v>453</v>
       </c>
       <c r="P54" s="25">
         <v>46332</v>
@@ -35965,432 +35896,432 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="B1" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="G2" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="H2" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="C3" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="F3" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="G3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="C4" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="D4" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="F4" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D5" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E5" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="F6" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="C7" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="D7" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="B8" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C8" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="D8" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="E8" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="F8" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B9" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="C9" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="D9" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="E9" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="D10" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="E10" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="F10" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="G10" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B11" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="D11" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="E11" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="B12" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="C12" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="D12" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="E12" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="B13" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="C13" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="D13" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="E13" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="B14" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C14" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="D14" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="E14" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="F14" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="B15" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="C15" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="D15" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="E15" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="B16" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D16" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="E16" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="B17" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="C17" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="D17" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="E17" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="F17" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="G17" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="B18" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="C18" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="D18" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="B19" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="C19" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="D19" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="E19" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="F19" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="G19" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="B20" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="D20" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="E20" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="F20" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="G20" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B21" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="C21" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="D21" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="E21" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F21" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="G21" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="B22" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="C22" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="D22" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="E22" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="B23" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="C23" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D23" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -36401,6 +36332,600 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25F8580F-4441-4D28-A88D-BD9653CD3E3D}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="106.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.5703125" customWidth="1"/>
+    <col min="6" max="6" width="66.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="26" customFormat="1" ht="15">
+      <c r="A1" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>477</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>479</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="32.25" customHeight="1">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>483</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="D2" s="29">
+        <v>46289</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>488</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="28">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="D3" s="29">
+        <v>46289</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>490</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="G3" s="28" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="28"/>
+      <c r="B4" s="13"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AD8B-A695-4A83-960F-4679E547561B}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+    <col min="4" max="4" width="67.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="26" customFormat="1" ht="15">
+      <c r="A1" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>494</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G2" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="28">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="D3" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G3" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="28">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G4" s="28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="28">
+        <v>4</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G5" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="28">
+        <v>5</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>507</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G6" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="28">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F7" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G7" s="28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="28">
+        <v>7</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G8" s="28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>525</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G9" s="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="28">
+        <v>9</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="E10" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F10" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G10" s="28">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="28">
+        <v>10</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>527</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G11" s="28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="28">
+        <v>11</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>530</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>529</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>528</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G12" s="28">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="28">
+        <v>12</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>533</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>531</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G13" s="28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="28">
+        <v>13</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>535</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>536</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>534</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G14" s="28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="28">
+        <v>14</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>539</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>537</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G15" s="28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="28">
+        <v>15</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>541</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>542</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>540</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G16" s="28">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="28">
+        <v>16</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>543</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G17" s="28">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="28">
+        <v>17</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>548</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G18" s="28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="28">
+        <v>18</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>550</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>551</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>549</v>
+      </c>
+      <c r="E19" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G19" s="28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="28">
+        <v>19</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>553</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>554</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>552</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>501</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>484</v>
+      </c>
+      <c r="G20" s="28">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="D21" s="28"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" display="https://nitori.sharepoint.com/:x:/r/sites/Teams__NTW/_layouts/15/Doc.aspx?sourcedoc=%7B101395D8-2FB4-4E6A-A962-B8DCCFBAB1F9%7D&amp;file=%25u671d%25u79ae-%25u9867%25u5ba2%25u6d3d%25u8ac7%25u5ba4%25u66a8%25u547c%25u53eb%25u4e2d%25u5fc3.xlsx&amp;action=default&amp;mobileredirect=true" xr:uid="{D332ACA5-9E74-442E-8CFF-D5783F276EBA}"/>
+    <hyperlink ref="D10" r:id="rId2" xr:uid="{32118B91-9B0B-46E5-8FE3-33F5B4C438AB}"/>
+    <hyperlink ref="D8" r:id="rId3" xr:uid="{5F05DAB7-97BA-49B5-910F-57BCBED08C31}"/>
+    <hyperlink ref="D6" r:id="rId4" location="/" xr:uid="{C81DE83B-EA8C-40F7-9078-AA80E46F091E}"/>
+    <hyperlink ref="D4" r:id="rId5" xr:uid="{C298346C-481A-49D2-AF49-10F8CA55A448}"/>
+    <hyperlink ref="D5" r:id="rId6" xr:uid="{F2D37E86-D0E2-43BD-A544-48B608FAEBFF}"/>
+    <hyperlink ref="D11" r:id="rId7" display="https://nitori.sharepoint.com/:x:/r/sites/Teams_9636966253/_layouts/15/Doc.aspx?sourcedoc=%7BD3289924-A2E6-4386-96BD-9711A177B131%7D&amp;file=%E2%96%A0%20%E9%A1%A7%E5%AE%A2%E5%95%8F%E9%A1%8C%E5%BD%99%E6%95%B4%E8%A8%98%E9%8C%84%E8%A1%A8.xlsx&amp;action=default&amp;mobileredirect=true" xr:uid="{60CD0A62-5642-4FB2-AE86-D15C6731EEEA}"/>
+    <hyperlink ref="D12" r:id="rId8" display="https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B481ED728-B16B-4F2D-9179-BD79134E81B0%7D&amp;file=%E9%96%80%E5%B8%82%E8%87%AA%E5%8F%96%E5%88%B0%E8%B2%A8%E5%95%8F%E9%A1%8C%E5%9B%9E%E5%A0%B1.xlsx&amp;action=default&amp;mobileredirect=true" xr:uid="{FF050955-60E0-4BCB-9482-780BEA73596D}"/>
+    <hyperlink ref="D13" r:id="rId9" display="https://nitori.sharepoint.com/:x:/s/Teams_-384/IQBOaMMnA7x1QZC6-4kKgLv-Af7TpbmlpptDofOrYKEIgxs?wdExp=TEAMS-TREATMENT&amp;web=1&amp;isSPOFile=1&amp;ovuser=94d67acc-8c17-4d3b-8463-9829cf08ef55%2Cchiaching_lin%40nitori.com.tw&amp;clickparams=eyJBcHBOYW1lIjoiVGVhbXMtRGVza3RvcCIsIkFwcFZlcnNpb24iOiI0OS8yNjA4MTMxOTMyMSIsIkhhc0ZlZGVyYXRlZFVzZXIiOmZhbHNlfQ%3D%3D" xr:uid="{9AF81959-8C5C-42CA-9DEE-C99DCD3B3001}"/>
+    <hyperlink ref="D14" r:id="rId10" display="https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B85DCED77-8281-4AD9-84EE-645E4378BB2D%7D&amp;file=%E7%9B%B4%E9%80%81%E6%89%98%E9%81%8B%E5%96%AE%E8%99%9F.xlsx&amp;action=default&amp;mobileredirect=true&amp;DefaultItemOpen=1&amp;ct=1735607179900&amp;wdOrigin=OFFICECOM-WEB.START.CONTENTACTIONS&amp;cid=ea813a7a-be11-41ac-b7e9-ee447bf0a5a2&amp;wdPreviousSessionSrc=HarmonyWeb&amp;wdPreviousSession=855bdce9-4bd9-49be-ae39-625e078be278" xr:uid="{CF466D04-826A-46C1-8BC2-E887B458A460}"/>
+    <hyperlink ref="D15" r:id="rId11" xr:uid="{420B29FB-C1C1-4DF2-8EBF-19AAE0A8B766}"/>
+    <hyperlink ref="D16" r:id="rId12" xr:uid="{854E844A-98F6-4D3A-8387-55FB877B926A}"/>
+    <hyperlink ref="D17" r:id="rId13" xr:uid="{6C3852E1-58D6-4072-9297-D3B297AE23F2}"/>
+    <hyperlink ref="D18" r:id="rId14" xr:uid="{033BE734-AC4F-4A41-A5B8-056EBDDEA081}"/>
+    <hyperlink ref="D19" r:id="rId15" xr:uid="{F0767104-C946-4838-89A5-96710DE0ED23}"/>
+    <hyperlink ref="D20" r:id="rId16" xr:uid="{0039D946-2755-48D2-A5F5-6E43E0E9307B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8286D452-541B-4D0F-8570-131AB8A429C1}">
   <dimension ref="A1:C58"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -36415,403 +36940,403 @@
         <v>1</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25" customHeight="1">
       <c r="A2" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5" customHeight="1">
       <c r="A3" s="18" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="18" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="18" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="21.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="18" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="18" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="18" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="B16" s="19" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="19" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="19" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="19" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="19" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="19" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="19" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="19" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" s="19" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" s="19" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" s="19" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="B27" s="19" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="B28" s="19" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" s="19" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="B30" s="19" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="B31" s="19" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="B32" s="19" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="19" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" s="19" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="19" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="19" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="19" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" s="19" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="19" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" s="19" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" s="19" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="2:2">
       <c r="B42" s="19" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="2:2">
       <c r="B43" s="19" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" s="19" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="2:2">
       <c r="B45" s="19" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="19" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" s="19" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" s="19" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49" spans="2:2">
       <c r="B49" s="19" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="50" spans="2:2">
       <c r="B50" s="19" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="2:2">
       <c r="B51" s="19" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="2:2">
       <c r="B52" s="19" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="53" spans="2:2">
       <c r="B53" s="19" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
     </row>
     <row r="54" spans="2:2">
       <c r="B54" s="19" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" s="19" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" s="19" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="19" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" s="19" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA7539F-6D14-40C2-8E7A-F4272DEFDE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B7A348-D0C1-4187-9B01-4BC5D1D54169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
@@ -3158,11 +3158,11 @@
     <t>影片說明</t>
   </si>
   <si>
-    <t>https://nitori.sharepoint.com/:v:/r/sites/Teams_9636966253/Shared%20Documents/%E3%80%90%E8%81%AF%E7%B5%A1%E3%80%91%E9%A1%A7%E5%AE%A2%E6%B4%BD%E8%AB%87%E5%AE%A4_%E9%A1%A7%E5%AE%A2%E6%A1%88%E4%BB%B6%E8%AB%AE%E8%A9%A2%E5%9B%9E%E5%A0%B1%E7%B3%BB%E7%B5%B1_%E5%AF%A6%E9%A9%97%E5%BA%97%E8%AA%AA%E6%98%8E.mp4?d=wa0d09fb824e54e0ba12f611e7b6def25&amp;csf=1&amp;web=1&amp;e=zM6swr</t>
+    <t>新人訓練影片</t>
+  </si>
+  <si>
+    <t>https://nitori.sharepoint.com/sites/Teams_9636966253/_layouts/15/stream.aspx?id=%2Fsites%2FTeams%5F9636966253%2FShared%20Documents%2F%E3%80%90%E8%81%AF%E7%B5%A1%E3%80%91%E9%A1%A7%E5%AE%A2%E6%B4%BD%E8%AB%87%E5%AE%A4%5F%E9%A1%A7%E5%AE%A2%E6%A1%88%E4%BB%B6%E8%AB%AE%E8%A9%A2%E5%9B%9E%E5%A0%B1%E7%B3%BB%E7%B5%B1%5F%E5%AF%A6%E9%A9%97%E5%BA%97%E8%AA%AA%E6%98%8E%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E13dbc629%2D2394%2D45fd%2Dbbe7%2De9f0f3ce901f</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新人訓練影片</t>
   </si>
 </sst>
 </file>
@@ -36989,13 +36989,13 @@
         <v>584</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C2" s="37" t="s">
         <v>633</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -38980,7 +38980,7 @@
       </c>
       <c r="G9" s="32"/>
     </row>
-    <row r="10" spans="1:7" ht="30">
+    <row r="10" spans="1:7">
       <c r="A10" s="37" t="s">
         <v>642</v>
       </c>
@@ -39041,7 +39041,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30">
+    <row r="13" spans="1:7">
       <c r="A13" s="37" t="s">
         <v>646</v>
       </c>
@@ -39061,7 +39061,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30">
+    <row r="14" spans="1:7">
       <c r="A14" s="37" t="s">
         <v>648</v>
       </c>
@@ -41763,7 +41763,7 @@
     <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="26" customFormat="1" ht="30">
+    <row r="1" spans="1:11" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
         <v>614</v>
       </c>
@@ -41806,6 +41806,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
@@ -41814,15 +41823,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42027,20 +42027,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
     <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B7A348-D0C1-4187-9B01-4BC5D1D54169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D05DD5A-79D1-453C-868E-7AB1BA611C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="925">
   <si>
     <t>序號</t>
   </si>
@@ -3162,6 +3162,30 @@
   </si>
   <si>
     <t>https://nitori.sharepoint.com/sites/Teams_9636966253/_layouts/15/stream.aspx?id=%2Fsites%2FTeams%5F9636966253%2FShared%20Documents%2F%E3%80%90%E8%81%AF%E7%B5%A1%E3%80%91%E9%A1%A7%E5%AE%A2%E6%B4%BD%E8%AB%87%E5%AE%A4%5F%E9%A1%A7%E5%AE%A2%E6%A1%88%E4%BB%B6%E8%AB%AE%E8%A9%A2%E5%9B%9E%E5%A0%B1%E7%B3%BB%E7%B5%B1%5F%E5%AF%A6%E9%A9%97%E5%BA%97%E8%AA%AA%E6%98%8E%2Emp4&amp;referrer=StreamWebApp%2EWeb&amp;referrerScenario=AddressBarCopied%2Eview%2E13dbc629%2D2394%2D45fd%2Dbbe7%2De9f0f3ce901f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>職稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部門</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到職日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>員工編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -37030,9 +37054,33 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCA3AC7-75B6-4A51-8714-4B2C3409730F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="26" customFormat="1" ht="30">
+      <c r="A1" s="39" t="s">
+        <v>924</v>
+      </c>
+      <c r="B1" s="39" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>920</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>921</v>
+      </c>
+      <c r="E1" s="39" t="s">
+        <v>922</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>923</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D05DD5A-79D1-453C-868E-7AB1BA611C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0EEA75-8D52-429C-B282-F0CF0E581659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="926">
   <si>
     <t>序號</t>
   </si>
@@ -2219,16 +2219,10 @@
     <t>解說</t>
   </si>
   <si>
-    <t>員工ID</t>
-  </si>
-  <si>
     <t>姓名</t>
   </si>
   <si>
     <t>學習狀態</t>
-  </si>
-  <si>
-    <t>測驗成績</t>
   </si>
   <si>
     <t>實作</t>
@@ -3186,6 +3180,17 @@
   </si>
   <si>
     <t>員工編號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開始日期</t>
+  </si>
+  <si>
+    <t>員工編號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>測驗狀態</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -36998,13 +37003,13 @@
         <v>578</v>
       </c>
       <c r="B1" s="39" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>913</v>
+      </c>
+      <c r="D1" s="39" t="s">
         <v>914</v>
-      </c>
-      <c r="C1" s="39" t="s">
-        <v>915</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>916</v>
       </c>
       <c r="E1" s="17"/>
     </row>
@@ -37013,13 +37018,13 @@
         <v>584</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -37060,24 +37065,24 @@
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="26" customFormat="1" ht="30">
+    <row r="1" spans="1:6" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B1" s="39" t="s">
+        <v>917</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>918</v>
+      </c>
+      <c r="D1" s="39" t="s">
         <v>919</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="E1" s="39" t="s">
         <v>920</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="F1" s="39" t="s">
         <v>921</v>
-      </c>
-      <c r="E1" s="39" t="s">
-        <v>922</v>
-      </c>
-      <c r="F1" s="39" t="s">
-        <v>923</v>
       </c>
     </row>
   </sheetData>
@@ -37093,10 +37098,10 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="17" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -37160,7 +37165,7 @@
         <v>583</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -37168,7 +37173,7 @@
         <v>583</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -37184,7 +37189,7 @@
         <v>582</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G12" s="36"/>
     </row>
@@ -37193,7 +37198,7 @@
         <v>606</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G13" s="36"/>
     </row>
@@ -37202,7 +37207,7 @@
         <v>606</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G14" s="36"/>
     </row>
@@ -37211,7 +37216,7 @@
         <v>606</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G15" s="36"/>
     </row>
@@ -38847,13 +38852,13 @@
         <v>579</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D1" s="39" t="s">
         <v>581</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F1" s="39" t="s">
         <v>583</v>
@@ -38868,7 +38873,7 @@
         <v>585</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D2" s="37">
         <v>1</v>
@@ -38877,7 +38882,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G2" s="32"/>
     </row>
@@ -38889,7 +38894,7 @@
         <v>585</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D3" s="37">
         <v>2</v>
@@ -38898,7 +38903,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G3" s="32"/>
     </row>
@@ -38919,19 +38924,19 @@
         <v>1</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B5" s="37" t="s">
         <v>585</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D5" s="37">
         <v>4</v>
@@ -38940,7 +38945,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G5" s="32"/>
     </row>
@@ -38952,7 +38957,7 @@
         <v>592</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D6" s="37">
         <v>5</v>
@@ -38961,7 +38966,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G6" s="32"/>
     </row>
@@ -38973,7 +38978,7 @@
         <v>592</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D7" s="37">
         <v>6</v>
@@ -38982,7 +38987,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G7" s="32"/>
     </row>
@@ -38994,7 +38999,7 @@
         <v>592</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D8" s="37">
         <v>7</v>
@@ -39003,19 +39008,19 @@
         <v>1</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="37" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B9" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D9" s="37">
         <v>8</v>
@@ -39024,19 +39029,19 @@
         <v>1</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B10" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D10" s="37">
         <v>9</v>
@@ -39045,13 +39050,13 @@
         <v>1</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="37" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B11" s="37" t="s">
         <v>592</v>
@@ -39066,18 +39071,18 @@
         <v>1</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B12" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D12" s="37">
         <v>11</v>
@@ -39086,18 +39091,18 @@
         <v>1</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B13" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D13" s="37">
         <v>12</v>
@@ -39106,18 +39111,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B14" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D14" s="37">
         <v>13</v>
@@ -39126,18 +39131,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B15" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D15" s="37">
         <v>14</v>
@@ -39146,18 +39151,18 @@
         <v>1</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B16" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D16" s="37">
         <v>15</v>
@@ -39166,18 +39171,18 @@
         <v>1</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B17" s="37" t="s">
         <v>592</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D17" s="37">
         <v>16</v>
@@ -39186,7 +39191,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -39197,7 +39202,7 @@
         <v>596</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D18" s="37">
         <v>17</v>
@@ -39206,7 +39211,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -39217,7 +39222,7 @@
         <v>596</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D19" s="37">
         <v>18</v>
@@ -39226,7 +39231,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -39237,7 +39242,7 @@
         <v>596</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D20" s="37">
         <v>19</v>
@@ -39246,18 +39251,18 @@
         <v>1</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="37" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B21" s="37" t="s">
         <v>596</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D21" s="37">
         <v>20</v>
@@ -39266,18 +39271,18 @@
         <v>1</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B22" s="37" t="s">
         <v>596</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D22" s="37">
         <v>21</v>
@@ -39286,18 +39291,18 @@
         <v>1</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B23" s="37" t="s">
         <v>596</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D23" s="37">
         <v>22</v>
@@ -39306,7 +39311,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>
@@ -39338,10 +39343,10 @@
         <v>599</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E1" s="39" t="s">
         <v>600</v>
@@ -39356,13 +39361,13 @@
         <v>584</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E2" s="37"/>
       <c r="F2" s="37">
@@ -39384,10 +39389,10 @@
         <v>602</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E3" s="37"/>
       <c r="F3" s="37">
@@ -39406,13 +39411,13 @@
         <v>584</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E4" s="37"/>
       <c r="F4" s="37">
@@ -39431,13 +39436,13 @@
         <v>584</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="37">
@@ -39456,13 +39461,13 @@
         <v>584</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E6" s="38"/>
       <c r="F6" s="37">
@@ -39481,13 +39486,13 @@
         <v>584</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="37">
@@ -39506,13 +39511,13 @@
         <v>588</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="37">
@@ -39534,10 +39539,10 @@
         <v>603</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="37">
@@ -39556,13 +39561,13 @@
         <v>588</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="37">
@@ -39581,13 +39586,13 @@
         <v>588</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E11" s="38"/>
       <c r="F11" s="37">
@@ -39606,13 +39611,13 @@
         <v>588</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="37">
@@ -39631,13 +39636,13 @@
         <v>589</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C13" s="37" t="s">
         <v>590</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="37">
@@ -39656,13 +39661,13 @@
         <v>589</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C14" s="37" t="s">
         <v>590</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E14" s="38"/>
       <c r="F14" s="37">
@@ -39681,13 +39686,13 @@
         <v>589</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C15" s="37" t="s">
         <v>590</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="37">
@@ -39703,16 +39708,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E16" s="38"/>
       <c r="F16" s="37">
@@ -39727,16 +39732,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E17" s="38"/>
       <c r="F17" s="37">
@@ -39751,16 +39756,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E18" s="38"/>
       <c r="F18" s="37">
@@ -39775,16 +39780,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E19" s="38"/>
       <c r="F19" s="37">
@@ -39793,7 +39798,7 @@
       <c r="J19" s="35"/>
       <c r="K19" s="35"/>
       <c r="L19" s="35" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="M19" s="35"/>
       <c r="N19" s="35"/>
@@ -39801,16 +39806,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="37">
@@ -39825,16 +39830,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="37">
@@ -39843,16 +39848,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="37">
@@ -39861,16 +39866,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="37">
@@ -39879,16 +39884,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="37">
@@ -39897,16 +39902,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="37" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="37">
@@ -39918,13 +39923,13 @@
         <v>591</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="37">
@@ -39939,10 +39944,10 @@
         <v>604</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="37">
@@ -39954,13 +39959,13 @@
         <v>591</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="37">
@@ -39972,13 +39977,13 @@
         <v>593</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="37">
@@ -39990,13 +39995,13 @@
         <v>593</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="37">
@@ -40008,13 +40013,13 @@
         <v>593</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="37">
@@ -40026,13 +40031,13 @@
         <v>593</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="37">
@@ -40044,13 +40049,13 @@
         <v>594</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38">
@@ -40062,13 +40067,13 @@
         <v>594</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38">
@@ -40080,13 +40085,13 @@
         <v>594</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38">
@@ -40098,13 +40103,13 @@
         <v>594</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38">
@@ -40116,13 +40121,13 @@
         <v>594</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38">
@@ -40131,16 +40136,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="37" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38">
@@ -40149,16 +40154,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="37" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38">
@@ -40167,16 +40172,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="37" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38">
@@ -40185,16 +40190,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="37" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38">
@@ -40203,16 +40208,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="37" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38">
@@ -40221,16 +40226,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38">
@@ -40239,16 +40244,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="37">
@@ -40257,16 +40262,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="37">
@@ -40275,16 +40280,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38">
@@ -40293,16 +40298,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B47" s="37" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="37">
@@ -40311,16 +40316,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="37">
@@ -40329,16 +40334,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B49" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="37">
@@ -40347,16 +40352,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B50" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="37">
@@ -40365,16 +40370,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="37" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B51" s="37" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="37">
@@ -40383,16 +40388,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="37" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="37">
@@ -40401,16 +40406,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="37" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="37">
@@ -40419,16 +40424,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="37" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="37">
@@ -40437,16 +40442,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="37">
@@ -40455,16 +40460,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B56" s="37" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="37">
@@ -40473,16 +40478,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B57" s="37" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="37">
@@ -40491,16 +40496,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B58" s="37" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="37">
@@ -40509,16 +40514,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B59" s="37" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="37">
@@ -40527,16 +40532,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B60" s="37" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="37">
@@ -40545,16 +40550,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="37" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B61" s="37" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D61" s="37" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="37">
@@ -40563,16 +40568,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B62" s="37" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D62" s="37" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="37">
@@ -40581,16 +40586,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C63" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="37">
@@ -40599,16 +40604,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="37">
@@ -40617,16 +40622,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B65" s="37" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="37">
@@ -40635,16 +40640,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="37">
@@ -40653,16 +40658,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="37">
@@ -40671,16 +40676,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="37" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="37">
@@ -40689,16 +40694,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="37">
@@ -40707,16 +40712,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B70" s="37" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C70" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="37">
@@ -40725,16 +40730,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B71" s="37" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C71" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="37">
@@ -40743,16 +40748,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B72" s="37" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C72" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="37">
@@ -40761,16 +40766,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B73" s="37" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="37">
@@ -40779,16 +40784,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B74" s="37" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C74" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="37">
@@ -40797,16 +40802,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B75" s="37" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D75" s="37" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="37">
@@ -40815,16 +40820,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="37" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B76" s="37" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="37">
@@ -40833,16 +40838,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B77" s="37" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D77" s="37" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="37">
@@ -40851,16 +40856,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B78" s="37" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C78" s="37" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="37">
@@ -40869,16 +40874,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C79" s="37" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E79" s="38"/>
       <c r="F79" s="37">
@@ -40887,16 +40892,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C80" s="37" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E80" s="38"/>
       <c r="F80" s="37">
@@ -40905,16 +40910,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B81" s="37" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D81" s="37" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E81" s="38"/>
       <c r="F81" s="37">
@@ -40923,16 +40928,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B82" s="37" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="37">
@@ -40941,16 +40946,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B83" s="37" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D83" s="37" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E83" s="38"/>
       <c r="F83" s="37">
@@ -40959,16 +40964,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B84" s="37" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C84" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E84" s="38"/>
       <c r="F84" s="37">
@@ -40977,16 +40982,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B85" s="37" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C85" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="37">
@@ -40995,16 +41000,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C86" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="37">
@@ -41013,16 +41018,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="E87" s="38"/>
       <c r="F87" s="37">
@@ -41031,16 +41036,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B88" s="37" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="E88" s="38"/>
       <c r="F88" s="37">
@@ -41049,16 +41054,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B89" s="37" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D89" s="37" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="37">
@@ -41067,16 +41072,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B90" s="37" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D90" s="37" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E90" s="38"/>
       <c r="F90" s="37">
@@ -41085,16 +41090,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B91" s="37" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D91" s="37" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E91" s="38"/>
       <c r="F91" s="37">
@@ -41103,16 +41108,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B92" s="37" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C92" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D92" s="37" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E92" s="38"/>
       <c r="F92" s="37">
@@ -41121,16 +41126,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B93" s="37" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C93" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D93" s="37" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E93" s="38"/>
       <c r="F93" s="37">
@@ -41139,16 +41144,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B94" s="37" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C94" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E94" s="38"/>
       <c r="F94" s="37">
@@ -41157,16 +41162,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B95" s="37" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C95" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D95" s="37" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E95" s="38"/>
       <c r="F95" s="37">
@@ -41175,16 +41180,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="37" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B96" s="37" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C96" s="37" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D96" s="37" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E96" s="38"/>
       <c r="F96" s="37">
@@ -41196,13 +41201,13 @@
         <v>595</v>
       </c>
       <c r="B97" s="37" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C97" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D97" s="37" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E97" s="38"/>
       <c r="F97" s="37">
@@ -41214,13 +41219,13 @@
         <v>595</v>
       </c>
       <c r="B98" s="37" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D98" s="37" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E98" s="38"/>
       <c r="F98" s="37">
@@ -41232,13 +41237,13 @@
         <v>595</v>
       </c>
       <c r="B99" s="37" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D99" s="37" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="E99" s="38"/>
       <c r="F99" s="37">
@@ -41250,13 +41255,13 @@
         <v>595</v>
       </c>
       <c r="B100" s="37" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D100" s="37" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E100" s="38"/>
       <c r="F100" s="37">
@@ -41268,13 +41273,13 @@
         <v>595</v>
       </c>
       <c r="B101" s="37" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C101" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D101" s="37" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E101" s="38"/>
       <c r="F101" s="37">
@@ -41286,13 +41291,13 @@
         <v>595</v>
       </c>
       <c r="B102" s="37" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E102" s="38"/>
       <c r="F102" s="37">
@@ -41304,13 +41309,13 @@
         <v>595</v>
       </c>
       <c r="B103" s="37" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C103" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D103" s="37" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E103" s="38"/>
       <c r="F103" s="37">
@@ -41322,13 +41327,13 @@
         <v>595</v>
       </c>
       <c r="B104" s="37" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D104" s="37" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E104" s="38"/>
       <c r="F104" s="37">
@@ -41340,13 +41345,13 @@
         <v>595</v>
       </c>
       <c r="B105" s="37" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E105" s="38"/>
       <c r="F105" s="37">
@@ -41358,13 +41363,13 @@
         <v>597</v>
       </c>
       <c r="B106" s="37" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C106" s="37" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D106" s="37" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E106" s="38"/>
       <c r="F106" s="37">
@@ -41376,13 +41381,13 @@
         <v>597</v>
       </c>
       <c r="B107" s="37" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D107" s="37" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E107" s="38"/>
       <c r="F107" s="37">
@@ -41394,13 +41399,13 @@
         <v>597</v>
       </c>
       <c r="B108" s="37" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D108" s="37" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E108" s="38"/>
       <c r="F108" s="37">
@@ -41412,13 +41417,13 @@
         <v>598</v>
       </c>
       <c r="B109" s="37" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D109" s="37" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E109" s="38"/>
       <c r="F109" s="37">
@@ -41430,13 +41435,13 @@
         <v>598</v>
       </c>
       <c r="B110" s="37" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C110" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D110" s="37" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E110" s="38"/>
       <c r="F110" s="37">
@@ -41448,13 +41453,13 @@
         <v>598</v>
       </c>
       <c r="B111" s="37" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C111" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D111" s="37" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E111" s="38"/>
       <c r="F111" s="37">
@@ -41466,13 +41471,13 @@
         <v>598</v>
       </c>
       <c r="B112" s="37" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C112" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D112" s="37" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E112" s="38"/>
       <c r="F112" s="37">
@@ -41484,13 +41489,13 @@
         <v>598</v>
       </c>
       <c r="B113" s="37" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C113" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D113" s="37" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E113" s="38"/>
       <c r="F113" s="37">
@@ -41502,13 +41507,13 @@
         <v>598</v>
       </c>
       <c r="B114" s="37" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C114" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D114" s="37" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E114" s="38"/>
       <c r="F114" s="37">
@@ -41520,13 +41525,13 @@
         <v>598</v>
       </c>
       <c r="B115" s="37" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C115" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D115" s="37" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E115" s="38"/>
       <c r="F115" s="37">
@@ -41535,16 +41540,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="37" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B116" s="37" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D116" s="37" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E116" s="38"/>
       <c r="F116" s="37">
@@ -41553,16 +41558,16 @@
     </row>
     <row r="117" spans="1:6" ht="30">
       <c r="A117" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B117" s="37" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D117" s="37" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E117" s="38"/>
       <c r="F117" s="37">
@@ -41571,16 +41576,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B118" s="37" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D118" s="37" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E118" s="38"/>
       <c r="F118" s="37">
@@ -41589,16 +41594,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B119" s="37" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D119" s="37" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E119" s="38"/>
       <c r="F119" s="37">
@@ -41607,16 +41612,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B120" s="37" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D120" s="37" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E120" s="38"/>
       <c r="F120" s="37">
@@ -41625,16 +41630,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B121" s="37" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D121" s="37" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E121" s="38"/>
       <c r="F121" s="37">
@@ -41643,16 +41648,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B122" s="37" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C122" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D122" s="37" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E122" s="38"/>
       <c r="F122" s="37">
@@ -41661,16 +41666,16 @@
     </row>
     <row r="123" spans="1:6" ht="30">
       <c r="A123" s="37" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B123" s="37" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D123" s="37" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E123" s="38"/>
       <c r="F123" s="37">
@@ -41679,16 +41684,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B124" s="37" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C124" s="37" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D124" s="37" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E124" s="38"/>
       <c r="F124" s="37">
@@ -41697,16 +41702,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B125" s="37" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C125" s="37" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D125" s="37" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E125" s="38"/>
       <c r="F125" s="37">
@@ -41715,16 +41720,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B126" s="37" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="C126" s="37" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D126" s="37" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E126" s="38"/>
       <c r="F126" s="37">
@@ -41801,22 +41806,24 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EDCA88-E8B5-4635-BFAB-48928384553D}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
     <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="26" customFormat="1" ht="15">
+    <row r="1" spans="1:12" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
+        <v>924</v>
+      </c>
+      <c r="B1" s="39" t="s">
         <v>614</v>
-      </c>
-      <c r="B1" s="39" t="s">
-        <v>615</v>
       </c>
       <c r="C1" s="39" t="s">
         <v>578</v>
@@ -41828,28 +41835,32 @@
         <v>579</v>
       </c>
       <c r="F1" s="39" t="s">
+        <v>923</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>615</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>925</v>
+      </c>
+      <c r="I1" s="39" t="s">
         <v>616</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="J1" s="39" t="s">
         <v>617</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="K1" s="39" t="s">
         <v>618</v>
       </c>
-      <c r="I1" s="39" t="s">
-        <v>619</v>
-      </c>
-      <c r="J1" s="39" t="s">
-        <v>620</v>
-      </c>
-      <c r="K1" s="17"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="J2" s="33"/>
+      <c r="L1" s="17"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="K2" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -41863,17 +41874,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16bed903-0179-4e60-92c1-b9da8d5f7bbf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010064913C44E1F1CB4CB693756E7EC2D392" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ca67994ffd5ed131a557285f1e41756c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="16bed903-0179-4e60-92c1-b9da8d5f7bbf" xmlns:ns3="2b5b1759-8281-4e33-bc6b-4f502641d3cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa37a9092383deea460b40ff1715ceb" ns2:_="" ns3:_="">
     <xsd:import namespace="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
@@ -42074,6 +42074,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16bed903-0179-4e60-92c1-b9da8d5f7bbf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
   <ds:schemaRefs>
@@ -42083,17 +42094,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
-    <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6479191D-8696-400D-B5CD-A3DAFAE30633}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42110,4 +42110,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
+    <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0EEA75-8D52-429C-B282-F0CF0E581659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE919F8D-8ACC-46E0-8773-49D620913B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="927">
   <si>
     <t>序號</t>
   </si>
@@ -3191,6 +3191,10 @@
   </si>
   <si>
     <t>測驗狀態</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>請問下列哪一個是七大畫法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -41757,9 +41761,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B29190-531C-4EA5-8672-32C9D5243721}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -41798,9 +41803,43 @@
         <v>601</v>
       </c>
     </row>
+    <row r="2" spans="1:11" ht="60">
+      <c r="A2" s="37">
+        <v>1</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>631</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>926</v>
+      </c>
+      <c r="E2" s="37">
+        <v>1</v>
+      </c>
+      <c r="F2" s="37">
+        <v>2</v>
+      </c>
+      <c r="G2" s="37">
+        <v>3</v>
+      </c>
+      <c r="H2" s="37">
+        <v>4</v>
+      </c>
+      <c r="I2" s="37">
+        <v>4</v>
+      </c>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -41904,12 +41904,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16bed903-0179-4e60-92c1-b9da8d5f7bbf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -42114,20 +42116,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16bed903-0179-4e60-92c1-b9da8d5f7bbf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
+    <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -42152,12 +42155,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
-    <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE919F8D-8ACC-46E0-8773-49D620913B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4392538-5514-4343-A9CA-097882284BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1588" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="928">
   <si>
     <t>序號</t>
   </si>
@@ -3195,6 +3195,10 @@
   </si>
   <si>
     <t>請問下列哪一個是七大畫法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林珈青</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -41894,6 +41898,12 @@
       <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12">
+      <c r="A2">
+        <v>2507238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>927</v>
+      </c>
       <c r="K2" s="33"/>
     </row>
   </sheetData>
@@ -41915,6 +41925,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010064913C44E1F1CB4CB693756E7EC2D392" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ca67994ffd5ed131a557285f1e41756c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="16bed903-0179-4e60-92c1-b9da8d5f7bbf" xmlns:ns3="2b5b1759-8281-4e33-bc6b-4f502641d3cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa37a9092383deea460b40ff1715ceb" ns2:_="" ns3:_="">
     <xsd:import namespace="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
@@ -42115,15 +42134,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
   <ds:schemaRefs>
@@ -42136,6 +42146,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6479191D-8696-400D-B5CD-A3DAFAE30633}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42152,12 +42170,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4392538-5514-4343-A9CA-097882284BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C991C6-518B-4F59-88C2-D87DABF5C14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="929">
   <si>
     <t>序號</t>
   </si>
@@ -3199,6 +3199,10 @@
   </si>
   <si>
     <t>林珈青</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -41832,8 +41836,8 @@
       <c r="H2" s="37">
         <v>4</v>
       </c>
-      <c r="I2" s="37">
-        <v>4</v>
+      <c r="I2" s="37" t="s">
+        <v>928</v>
       </c>
       <c r="J2" s="37"/>
       <c r="K2" s="37">
@@ -41925,15 +41929,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010064913C44E1F1CB4CB693756E7EC2D392" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ca67994ffd5ed131a557285f1e41756c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="16bed903-0179-4e60-92c1-b9da8d5f7bbf" xmlns:ns3="2b5b1759-8281-4e33-bc6b-4f502641d3cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa37a9092383deea460b40ff1715ceb" ns2:_="" ns3:_="">
     <xsd:import namespace="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
@@ -42134,6 +42129,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
   <ds:schemaRefs>
@@ -42146,14 +42150,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6479191D-8696-400D-B5CD-A3DAFAE30633}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42170,4 +42166,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C991C6-518B-4F59-88C2-D87DABF5C14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3FAC5F-80CD-4B84-91D4-B2D8A2083BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="11" r:id="rId1"/>
     <sheet name="搜尋詞對照" sheetId="14" r:id="rId2"/>
     <sheet name="內部公告" sheetId="15" r:id="rId3"/>
-    <sheet name="常用工具" sheetId="16" r:id="rId4"/>
+    <sheet name="系統索引" sheetId="30" r:id="rId4"/>
     <sheet name="客訴資料" sheetId="17" r:id="rId5"/>
     <sheet name="課程總表" sheetId="18" r:id="rId6"/>
     <sheet name="課程內容" sheetId="19" r:id="rId7"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="883">
   <si>
     <t>序號</t>
   </si>
@@ -1731,9 +1731,6 @@
   </si>
   <si>
     <t>顯示</t>
-  </si>
-  <si>
-    <t>顯示</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1767,236 +1764,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>工具編號</t>
-  </si>
-  <si>
-    <t>工具名稱</t>
-  </si>
-  <si>
-    <t>工具說明</t>
-  </si>
-  <si>
-    <t>工具網址</t>
-  </si>
-  <si>
-    <t>顯示順序</t>
-  </si>
-  <si>
-    <t>工具分類</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顯示狀態</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Teams</t>
-  </si>
-  <si>
-    <t>內部系統</t>
-  </si>
-  <si>
-    <t>客服信箱</t>
-  </si>
-  <si>
-    <t>PChome</t>
-  </si>
-  <si>
-    <t>網購訂單查詢</t>
-  </si>
-  <si>
-    <t>網購平台</t>
-  </si>
-  <si>
-    <t>MOMO</t>
-  </si>
-  <si>
-    <t>Rakuten</t>
-  </si>
-  <si>
     <t>COMPANY</t>
-  </si>
-  <si>
-    <t>公司內部系統</t>
-  </si>
-  <si>
-    <t>官網後台</t>
-  </si>
-  <si>
-    <t>X</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服務信箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitori.sharepoint.com/:x:/r/sites/Teams__NTW/_layouts/15/Doc.aspx?sourcedoc=%7B101395D8-2FB4-4E6A-A962-B8DCCFBAB1F9%7D&amp;file=%25u671d%25u79ae-%25u9867%25u5ba2%25u6d3d%25u8ac7%25u5ba4%25u66a8%25u547c%25u53eb%25u4e2d%25u5fc3.xlsx&amp;action=default&amp;mobileredirect=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>洽談室朝禮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>洽談室班表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitori.sharepoint.com/:x:/r/sites/Teams_9636966253/_layouts/15/Doc.aspx?sourcedoc=%7BB230F05C-0764-4E6D-82B7-1411871B08FC%7D&amp;file=%E9%A1%A7%E5%AE%A2%E6%B4%BD%E8%AB%87%E5%AE%A4%E7%8F%AD%E8%A1%A82026.xlsx&amp;action=default&amp;mobileredirect=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitoribackendwin.azurewebsites.net/dashboard</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://rms.rakuten.com.tw/login#/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ecvdr.pchome.com.tw/v2016/login/v1/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://scm.momoshop.com.tw/manage/login.jsp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitori.sharepoint.com/:x:/r/sites/Teams_9636966253/_layouts/15/Doc.aspx?sourcedoc=%7BD3289924-A2E6-4386-96BD-9711A177B131%7D&amp;file=%E2%96%A0%20%E9%A1%A7%E5%AE%A2%E5%95%8F%E9%A1%8C%E5%BD%99%E6%95%B4%E8%A8%98%E9%8C%84%E8%A1%A8.xlsx&amp;action=default&amp;mobileredirect=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顧客問題彙整記錄表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表單</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顧客問題回覆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每日宣達</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大家ㄟ班表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>非電話紀錄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B481ED728-B16B-4F2D-9179-BD79134E81B0%7D&amp;file=%E9%96%80%E5%B8%82%E8%87%AA%E5%8F%96%E5%88%B0%E8%B2%A8%E5%95%8F%E9%A1%8C%E5%9B%9E%E5%A0%B1.xlsx&amp;action=default&amp;mobileredirect=true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>門市自取用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>門市自取問題回報表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitori.sharepoint.com/:x:/s/Teams_-384/IQBOaMMnA7x1QZC6-4kKgLv-Af7TpbmlpptDofOrYKEIgxs?wdExp=TEAMS-TREATMENT&amp;web=1&amp;isSPOFile=1&amp;ovuser=94d67acc-8c17-4d3b-8463-9829cf08ef55%2Cchiaching_lin%40nitori.com.tw&amp;clickparams=eyJBcHBOYW1lIjoiVGVhbXMtRGVza3RvcCIsIkFwcFZlcnNpb24iOiI0OS8yNjA4MTMxOTMyMSIsIkhhc0ZlZGVyYXRlZFVzZXIiOmZhbHNlfQ%3D%3D</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>網購售後用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>售後清單</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B85DCED77-8281-4AD9-84EE-645E4378BB2D%7D&amp;file=%E7%9B%B4%E9%80%81%E6%89%98%E9%81%8B%E5%96%AE%E8%99%9F.xlsx&amp;action=default&amp;mobileredirect=true&amp;DefaultItemOpen=1&amp;ct=1735607179900&amp;wdOrigin=OFFICECOM-WEB.START.CONTENTACTIONS&amp;cid=ea813a7a-be11-41ac-b7e9-ee447bf0a5a2&amp;wdPreviousSessionSrc=HarmonyWeb&amp;wdPreviousSession=855bdce9-4bd9-49be-ae39-625e078be278</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直送托運單</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC直送查單號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://ecmerchant.nccc.com.tw/ecmht/LoginMerchant.NCCC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NCCC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查官網信用卡交易紀錄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.bpscm.com.tw/ASP/Login/Login.aspx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金財通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>發票寄出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://sms.mitake.com.tw/common/index.jsp?t=1790222541479</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>寄送簡訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三竹簡訊</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://content.nitori-net.tw/nitorihome/common/imgcatch2.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多品抓圖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同時搜尋多樣商品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://forms.cloud.microsoft/pages/responsepage.aspx?id=zHrWlBeMO02EY5gpzwjvVdSWENxQ1_VFnSafIvPS9t9UMEpRRklEVkpVSFBYUzdHUllMWEw5MkIwRiQlQCN0PWcu&amp;route=shorturl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配送意見回覆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配送中心或配送員客訴</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://apsweb.hct.com.tw/SCTM/</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新竹物流後台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>查詢每日配送的紀錄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>日期</t>
@@ -3203,6 +2971,60 @@
   </si>
   <si>
     <t>D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名稱</t>
+  </si>
+  <si>
+    <t>類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用途</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作截圖</t>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-F1  商品資訊查詢</t>
+  </si>
+  <si>
+    <t>1-F10 客戶傳票資訊查詢</t>
+  </si>
+  <si>
+    <t>2-F1 收銀小票搜尋</t>
+  </si>
+  <si>
+    <t>2-F5 商品庫存查詢</t>
+  </si>
+  <si>
+    <t>2-F9 捆包商品資訊查詢</t>
+  </si>
+  <si>
+    <t>3-F5 POP列印</t>
+  </si>
+  <si>
+    <t>13-F11 客戶配送資訊管理</t>
+  </si>
+  <si>
+    <t>18-F8 客戶傳票管理</t>
+  </si>
+  <si>
+    <t>系統</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林珈青</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3911,7 +3733,7 @@
         <v>449</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>557</v>
+        <v>495</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
@@ -3959,7 +3781,7 @@
         <v>452</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>558</v>
+        <v>496</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
@@ -4045,7 +3867,7 @@
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3" t="s">
-        <v>559</v>
+        <v>497</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
@@ -4093,7 +3915,7 @@
         <v>457</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>560</v>
+        <v>498</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
@@ -4141,7 +3963,7 @@
         <v>458</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>561</v>
+        <v>499</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
@@ -4225,7 +4047,7 @@
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3" t="s">
-        <v>562</v>
+        <v>500</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
@@ -4271,7 +4093,7 @@
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3" t="s">
-        <v>563</v>
+        <v>501</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
@@ -4355,7 +4177,7 @@
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3" t="s">
-        <v>564</v>
+        <v>502</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
@@ -4429,17 +4251,17 @@
         <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>565</v>
+        <v>503</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>80</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>568</v>
+        <v>506</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3" t="s">
-        <v>569</v>
+        <v>507</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
@@ -4481,11 +4303,11 @@
         <v>82</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>567</v>
+        <v>505</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3" t="s">
-        <v>569</v>
+        <v>507</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
@@ -4521,21 +4343,21 @@
         <v>74</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>570</v>
+        <v>508</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>566</v>
+        <v>504</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>571</v>
+        <v>509</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>572</v>
+        <v>510</v>
       </c>
       <c r="N16" s="25">
         <v>45719</v>
@@ -4567,7 +4389,7 @@
         <v>74</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>573</v>
+        <v>511</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>75</v>
@@ -4577,7 +4399,7 @@
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>574</v>
+        <v>512</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
@@ -4613,7 +4435,7 @@
         <v>74</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>575</v>
+        <v>513</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>93</v>
@@ -4623,11 +4445,11 @@
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>577</v>
+        <v>515</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>576</v>
+        <v>514</v>
       </c>
       <c r="N18" s="25">
         <v>46061</v>
@@ -37012,31 +36834,31 @@
   <sheetData>
     <row r="1" spans="1:5" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
-        <v>578</v>
+        <v>516</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>912</v>
+        <v>850</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>913</v>
+        <v>851</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>914</v>
+        <v>852</v>
       </c>
       <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" ht="100.5" customHeight="1">
       <c r="A2" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>916</v>
+        <v>854</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>915</v>
+        <v>853</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -37071,7 +36893,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCA3AC7-75B6-4A51-8714-4B2C3409730F}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -37079,22 +36901,30 @@
   <sheetData>
     <row r="1" spans="1:6" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
-        <v>922</v>
+        <v>860</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>917</v>
+        <v>855</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>918</v>
+        <v>856</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>919</v>
+        <v>857</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>920</v>
+        <v>858</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>921</v>
+        <v>859</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="32" customFormat="1">
+      <c r="A2" s="32">
+        <v>2507238</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>882</v>
       </c>
     </row>
   </sheetData>
@@ -37110,39 +36940,39 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="17" t="s">
-        <v>619</v>
+        <v>557</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>620</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="31" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>585</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="31" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="31" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="31" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
       <c r="B5" s="31">
         <v>1</v>
@@ -37150,7 +36980,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="31" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
       <c r="B6" s="31">
         <v>2</v>
@@ -37158,7 +36988,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="31" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
       <c r="B7" s="31">
         <v>3</v>
@@ -37166,69 +36996,69 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="31" t="s">
-        <v>583</v>
+        <v>521</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>587</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="31" t="s">
-        <v>583</v>
+        <v>521</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>621</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="31" t="s">
-        <v>583</v>
+        <v>521</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>622</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="31" t="s">
-        <v>582</v>
+        <v>520</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>586</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="31" t="s">
-        <v>582</v>
+        <v>520</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>623</v>
+        <v>561</v>
       </c>
       <c r="G12" s="36"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="31" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>624</v>
+        <v>562</v>
       </c>
       <c r="G13" s="36"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="31" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>625</v>
+        <v>563</v>
       </c>
       <c r="G14" s="36"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="31" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>626</v>
+        <v>564</v>
       </c>
       <c r="G15" s="36"/>
     </row>
@@ -38190,19 +38020,19 @@
         <v>476</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D2" s="29">
         <v>46289</v>
       </c>
       <c r="E2" s="28" t="s">
+        <v>480</v>
+      </c>
+      <c r="F2" s="27" t="s">
         <v>481</v>
       </c>
-      <c r="F2" s="27" t="s">
-        <v>482</v>
-      </c>
       <c r="G2" s="28" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -38210,22 +38040,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D3" s="29">
         <v>46289</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F3" s="27" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -38239,502 +38069,100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AD8B-A695-4A83-960F-4679E547561B}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCCF2E1E-D7CC-4FF6-B911-5DC220498719}">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="28.28515625" customWidth="1"/>
-    <col min="4" max="4" width="67.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="26" customFormat="1" ht="15">
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="15">
       <c r="A1" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>487</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="28">
-        <v>1</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="E2" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G2" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="28">
-        <v>2</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>505</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G3" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="28">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G4" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="28">
-        <v>4</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>499</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="E5" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G5" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="28">
-        <v>5</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>511</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G6" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="28">
-        <v>6</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G7" s="28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="28">
-        <v>7</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>517</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>510</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G8" s="28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="28">
-        <v>8</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G9" s="28">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="28">
-        <v>9</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>519</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G10" s="28">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="28">
-        <v>10</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>515</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>514</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G11" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="28">
-        <v>11</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>523</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>522</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>521</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G12" s="28">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="28">
-        <v>12</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>526</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>525</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>524</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G13" s="28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="28">
-        <v>13</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>528</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>529</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>527</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G14" s="28">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="28">
-        <v>14</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>531</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>532</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>530</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G15" s="28">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="28">
-        <v>15</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>534</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>535</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>533</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G16" s="28">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="28">
-        <v>16</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>538</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>537</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>536</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G17" s="28">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="28">
-        <v>17</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>540</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>541</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>539</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G18" s="28">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="28">
-        <v>18</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>543</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>544</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>542</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G19" s="28">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="28">
-        <v>19</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>546</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>547</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>545</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>494</v>
-      </c>
-      <c r="F20" s="28" t="s">
-        <v>477</v>
-      </c>
-      <c r="G20" s="28">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="D21" s="28"/>
+        <v>867</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>868</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>869</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>870</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>871</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B2" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>875</v>
+      </c>
+      <c r="B4" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>876</v>
+      </c>
+      <c r="B5" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>877</v>
+      </c>
+      <c r="B6" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>878</v>
+      </c>
+      <c r="B7" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>879</v>
+      </c>
+      <c r="B8" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>880</v>
+      </c>
+      <c r="B9" t="s">
+        <v>881</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" display="https://nitori.sharepoint.com/:x:/r/sites/Teams__NTW/_layouts/15/Doc.aspx?sourcedoc=%7B101395D8-2FB4-4E6A-A962-B8DCCFBAB1F9%7D&amp;file=%25u671d%25u79ae-%25u9867%25u5ba2%25u6d3d%25u8ac7%25u5ba4%25u66a8%25u547c%25u53eb%25u4e2d%25u5fc3.xlsx&amp;action=default&amp;mobileredirect=true" xr:uid="{D332ACA5-9E74-442E-8CFF-D5783F276EBA}"/>
-    <hyperlink ref="D10" r:id="rId2" xr:uid="{32118B91-9B0B-46E5-8FE3-33F5B4C438AB}"/>
-    <hyperlink ref="D8" r:id="rId3" xr:uid="{5F05DAB7-97BA-49B5-910F-57BCBED08C31}"/>
-    <hyperlink ref="D6" r:id="rId4" location="/" xr:uid="{C81DE83B-EA8C-40F7-9078-AA80E46F091E}"/>
-    <hyperlink ref="D4" r:id="rId5" xr:uid="{C298346C-481A-49D2-AF49-10F8CA55A448}"/>
-    <hyperlink ref="D5" r:id="rId6" xr:uid="{F2D37E86-D0E2-43BD-A544-48B608FAEBFF}"/>
-    <hyperlink ref="D11" r:id="rId7" display="https://nitori.sharepoint.com/:x:/r/sites/Teams_9636966253/_layouts/15/Doc.aspx?sourcedoc=%7BD3289924-A2E6-4386-96BD-9711A177B131%7D&amp;file=%E2%96%A0%20%E9%A1%A7%E5%AE%A2%E5%95%8F%E9%A1%8C%E5%BD%99%E6%95%B4%E8%A8%98%E9%8C%84%E8%A1%A8.xlsx&amp;action=default&amp;mobileredirect=true" xr:uid="{60CD0A62-5642-4FB2-AE86-D15C6731EEEA}"/>
-    <hyperlink ref="D12" r:id="rId8" display="https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B481ED728-B16B-4F2D-9179-BD79134E81B0%7D&amp;file=%E9%96%80%E5%B8%82%E8%87%AA%E5%8F%96%E5%88%B0%E8%B2%A8%E5%95%8F%E9%A1%8C%E5%9B%9E%E5%A0%B1.xlsx&amp;action=default&amp;mobileredirect=true" xr:uid="{FF050955-60E0-4BCB-9482-780BEA73596D}"/>
-    <hyperlink ref="D13" r:id="rId9" display="https://nitori.sharepoint.com/:x:/s/Teams_-384/IQBOaMMnA7x1QZC6-4kKgLv-Af7TpbmlpptDofOrYKEIgxs?wdExp=TEAMS-TREATMENT&amp;web=1&amp;isSPOFile=1&amp;ovuser=94d67acc-8c17-4d3b-8463-9829cf08ef55%2Cchiaching_lin%40nitori.com.tw&amp;clickparams=eyJBcHBOYW1lIjoiVGVhbXMtRGVza3RvcCIsIkFwcFZlcnNpb24iOiI0OS8yNjA4MTMxOTMyMSIsIkhhc0ZlZGVyYXRlZFVzZXIiOmZhbHNlfQ%3D%3D" xr:uid="{9AF81959-8C5C-42CA-9DEE-C99DCD3B3001}"/>
-    <hyperlink ref="D14" r:id="rId10" display="https://nitori.sharepoint.com/:x:/r/teams/nitori_tw/tw_portal/_layouts/15/Doc.aspx?sourcedoc=%7B85DCED77-8281-4AD9-84EE-645E4378BB2D%7D&amp;file=%E7%9B%B4%E9%80%81%E6%89%98%E9%81%8B%E5%96%AE%E8%99%9F.xlsx&amp;action=default&amp;mobileredirect=true&amp;DefaultItemOpen=1&amp;ct=1735607179900&amp;wdOrigin=OFFICECOM-WEB.START.CONTENTACTIONS&amp;cid=ea813a7a-be11-41ac-b7e9-ee447bf0a5a2&amp;wdPreviousSessionSrc=HarmonyWeb&amp;wdPreviousSession=855bdce9-4bd9-49be-ae39-625e078be278" xr:uid="{CF466D04-826A-46C1-8BC2-E887B458A460}"/>
-    <hyperlink ref="D15" r:id="rId11" xr:uid="{420B29FB-C1C1-4DF2-8EBF-19AAE0A8B766}"/>
-    <hyperlink ref="D16" r:id="rId12" xr:uid="{854E844A-98F6-4D3A-8387-55FB877B926A}"/>
-    <hyperlink ref="D17" r:id="rId13" xr:uid="{6C3852E1-58D6-4072-9297-D3B297AE23F2}"/>
-    <hyperlink ref="D18" r:id="rId14" xr:uid="{033BE734-AC4F-4A41-A5B8-056EBDDEA081}"/>
-    <hyperlink ref="D19" r:id="rId15" xr:uid="{F0767104-C946-4838-89A5-96710DE0ED23}"/>
-    <hyperlink ref="D20" r:id="rId16" xr:uid="{0039D946-2755-48D2-A5F5-6E43E0E9307B}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -38759,13 +38187,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>548</v>
+        <v>486</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>549</v>
+        <v>487</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>556</v>
+        <v>494</v>
       </c>
       <c r="E1" s="39" t="s">
         <v>6</v>
@@ -38774,22 +38202,22 @@
         <v>4</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>550</v>
+        <v>488</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>551</v>
+        <v>489</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>552</v>
+        <v>490</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>553</v>
+        <v>491</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>554</v>
+        <v>492</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>555</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -38858,34 +38286,34 @@
   <sheetData>
     <row r="1" spans="1:7" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
-        <v>578</v>
+        <v>516</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>660</v>
+        <v>598</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>581</v>
+        <v>519</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>659</v>
+        <v>597</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>583</v>
+        <v>521</v>
       </c>
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>585</v>
+        <v>523</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D2" s="37">
         <v>1</v>
@@ -38894,19 +38322,19 @@
         <v>1</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G2" s="32"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="37" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>585</v>
+        <v>523</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D3" s="37">
         <v>2</v>
@@ -38915,19 +38343,19 @@
         <v>1</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G3" s="32"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="37" t="s">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>585</v>
+        <v>523</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>590</v>
+        <v>528</v>
       </c>
       <c r="D4" s="37">
         <v>3</v>
@@ -38936,19 +38364,19 @@
         <v>1</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G4" s="32"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>585</v>
+        <v>523</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D5" s="37">
         <v>4</v>
@@ -38957,19 +38385,19 @@
         <v>1</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G5" s="32"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="37" t="s">
-        <v>591</v>
+        <v>529</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="D6" s="37">
         <v>5</v>
@@ -38978,19 +38406,19 @@
         <v>1</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G6" s="32"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="37" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="D7" s="37">
         <v>6</v>
@@ -38999,19 +38427,19 @@
         <v>1</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G7" s="32"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="37" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="D8" s="37">
         <v>7</v>
@@ -39020,19 +38448,19 @@
         <v>1</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G8" s="32"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="37" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="D9" s="37">
         <v>8</v>
@@ -39041,19 +38469,19 @@
         <v>1</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G9" s="32"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D10" s="37">
         <v>9</v>
@@ -39062,19 +38490,19 @@
         <v>1</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="G10" s="32"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="37" t="s">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="D11" s="37">
         <v>10</v>
@@ -39083,18 +38511,18 @@
         <v>1</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>871</v>
+        <v>809</v>
       </c>
       <c r="D12" s="37">
         <v>11</v>
@@ -39103,18 +38531,18 @@
         <v>1</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D13" s="37">
         <v>12</v>
@@ -39123,18 +38551,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D14" s="37">
         <v>13</v>
@@ -39143,18 +38571,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="37" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="D15" s="37">
         <v>14</v>
@@ -39163,18 +38591,18 @@
         <v>1</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D16" s="37">
         <v>15</v>
@@ -39183,18 +38611,18 @@
         <v>1</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D17" s="37">
         <v>16</v>
@@ -39203,18 +38631,18 @@
         <v>1</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D18" s="37">
         <v>17</v>
@@ -39223,18 +38651,18 @@
         <v>1</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="37" t="s">
-        <v>597</v>
+        <v>535</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>653</v>
+        <v>591</v>
       </c>
       <c r="D19" s="37">
         <v>18</v>
@@ -39243,18 +38671,18 @@
         <v>1</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D20" s="37">
         <v>19</v>
@@ -39263,18 +38691,18 @@
         <v>1</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="37" t="s">
-        <v>655</v>
+        <v>593</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>656</v>
+        <v>594</v>
       </c>
       <c r="D21" s="37">
         <v>20</v>
@@ -39283,18 +38711,18 @@
         <v>1</v>
       </c>
       <c r="F21" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B22" s="37" t="s">
+        <v>534</v>
+      </c>
+      <c r="C22" s="37" t="s">
         <v>596</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>658</v>
       </c>
       <c r="D22" s="37">
         <v>21</v>
@@ -39303,18 +38731,18 @@
         <v>1</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="37" t="s">
-        <v>801</v>
+        <v>739</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>596</v>
+        <v>534</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="D23" s="37">
         <v>22</v>
@@ -39323,7 +38751,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -39349,37 +38777,37 @@
   <sheetData>
     <row r="1" spans="1:16" s="41" customFormat="1">
       <c r="A1" s="39" t="s">
-        <v>578</v>
+        <v>516</v>
       </c>
       <c r="B1" s="39" t="s">
+        <v>537</v>
+      </c>
+      <c r="C1" s="39" t="s">
+        <v>598</v>
+      </c>
+      <c r="D1" s="39" t="s">
         <v>599</v>
       </c>
-      <c r="C1" s="39" t="s">
-        <v>660</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>661</v>
-      </c>
       <c r="E1" s="39" t="s">
-        <v>600</v>
+        <v>538</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>815</v>
+        <v>753</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>809</v>
+        <v>747</v>
       </c>
       <c r="E2" s="37"/>
       <c r="F2" s="37">
@@ -39395,16 +38823,16 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>810</v>
+        <v>748</v>
       </c>
       <c r="E3" s="37"/>
       <c r="F3" s="37">
@@ -39420,16 +38848,16 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>662</v>
+        <v>600</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>811</v>
+        <v>749</v>
       </c>
       <c r="E4" s="37"/>
       <c r="F4" s="37">
@@ -39445,16 +38873,16 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>663</v>
+        <v>601</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>812</v>
+        <v>750</v>
       </c>
       <c r="E5" s="37"/>
       <c r="F5" s="37">
@@ -39470,16 +38898,16 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>664</v>
+        <v>602</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>813</v>
+        <v>751</v>
       </c>
       <c r="E6" s="38"/>
       <c r="F6" s="37">
@@ -39495,16 +38923,16 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>814</v>
+        <v>752</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="37">
@@ -39520,16 +38948,16 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="37" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>821</v>
+        <v>759</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>816</v>
+        <v>754</v>
       </c>
       <c r="E8" s="38"/>
       <c r="F8" s="37">
@@ -39545,16 +38973,16 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="37" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>603</v>
+        <v>541</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>817</v>
+        <v>755</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="37">
@@ -39570,16 +38998,16 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="37" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>666</v>
+        <v>604</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>818</v>
+        <v>756</v>
       </c>
       <c r="E10" s="38"/>
       <c r="F10" s="37">
@@ -39595,16 +39023,16 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="37" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>667</v>
+        <v>605</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>819</v>
+        <v>757</v>
       </c>
       <c r="E11" s="38"/>
       <c r="F11" s="37">
@@ -39620,16 +39048,16 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="37" t="s">
-        <v>588</v>
+        <v>526</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>668</v>
+        <v>606</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>820</v>
+        <v>758</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="37">
@@ -39645,16 +39073,16 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="37" t="s">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>781</v>
+        <v>719</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>590</v>
+        <v>528</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>822</v>
+        <v>760</v>
       </c>
       <c r="E13" s="38"/>
       <c r="F13" s="37">
@@ -39670,16 +39098,16 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="37" t="s">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>669</v>
+        <v>607</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>590</v>
+        <v>528</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>823</v>
+        <v>761</v>
       </c>
       <c r="E14" s="38"/>
       <c r="F14" s="37">
@@ -39695,16 +39123,16 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="37" t="s">
-        <v>589</v>
+        <v>527</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>670</v>
+        <v>608</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>590</v>
+        <v>528</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>824</v>
+        <v>762</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="37">
@@ -39720,16 +39148,16 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>782</v>
+        <v>720</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D16" s="37" t="s">
-        <v>825</v>
+        <v>763</v>
       </c>
       <c r="E16" s="38"/>
       <c r="F16" s="37">
@@ -39744,16 +39172,16 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>671</v>
+        <v>609</v>
       </c>
       <c r="C17" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>826</v>
+        <v>764</v>
       </c>
       <c r="E17" s="38"/>
       <c r="F17" s="37">
@@ -39768,16 +39196,16 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>672</v>
+        <v>610</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>827</v>
+        <v>765</v>
       </c>
       <c r="E18" s="38"/>
       <c r="F18" s="37">
@@ -39792,16 +39220,16 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B19" s="37" t="s">
-        <v>673</v>
+        <v>611</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>828</v>
+        <v>766</v>
       </c>
       <c r="E19" s="38"/>
       <c r="F19" s="37">
@@ -39810,7 +39238,7 @@
       <c r="J19" s="35"/>
       <c r="K19" s="35"/>
       <c r="L19" s="35" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="M19" s="35"/>
       <c r="N19" s="35"/>
@@ -39818,16 +39246,16 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>674</v>
+        <v>612</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>829</v>
+        <v>767</v>
       </c>
       <c r="E20" s="38"/>
       <c r="F20" s="37">
@@ -39842,16 +39270,16 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B21" s="37" t="s">
-        <v>675</v>
+        <v>613</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>830</v>
+        <v>768</v>
       </c>
       <c r="E21" s="38"/>
       <c r="F21" s="37">
@@ -39860,16 +39288,16 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>676</v>
+        <v>614</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>831</v>
+        <v>769</v>
       </c>
       <c r="E22" s="38"/>
       <c r="F22" s="37">
@@ -39878,16 +39306,16 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>677</v>
+        <v>615</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D23" s="37" t="s">
-        <v>832</v>
+        <v>770</v>
       </c>
       <c r="E23" s="38"/>
       <c r="F23" s="37">
@@ -39896,16 +39324,16 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>678</v>
+        <v>616</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>833</v>
+        <v>771</v>
       </c>
       <c r="E24" s="38"/>
       <c r="F24" s="37">
@@ -39914,16 +39342,16 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="37" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>679</v>
+        <v>617</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>911</v>
+        <v>849</v>
       </c>
       <c r="E25" s="38"/>
       <c r="F25" s="37">
@@ -39932,16 +39360,16 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="37" t="s">
-        <v>591</v>
+        <v>529</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>784</v>
+        <v>722</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>834</v>
+        <v>772</v>
       </c>
       <c r="E26" s="38"/>
       <c r="F26" s="37">
@@ -39950,16 +39378,16 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="37" t="s">
-        <v>591</v>
+        <v>529</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>604</v>
+        <v>542</v>
       </c>
       <c r="C27" s="37" t="s">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="D27" s="37" t="s">
-        <v>835</v>
+        <v>773</v>
       </c>
       <c r="E27" s="38"/>
       <c r="F27" s="37">
@@ -39968,16 +39396,16 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="37" t="s">
-        <v>591</v>
+        <v>529</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>680</v>
+        <v>618</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="D28" s="37" t="s">
-        <v>836</v>
+        <v>774</v>
       </c>
       <c r="E28" s="38"/>
       <c r="F28" s="37">
@@ -39986,16 +39414,16 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="37" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="B29" s="37" t="s">
-        <v>783</v>
+        <v>721</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>837</v>
+        <v>775</v>
       </c>
       <c r="E29" s="38"/>
       <c r="F29" s="37">
@@ -40004,16 +39432,16 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="37" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>681</v>
+        <v>619</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>838</v>
+        <v>776</v>
       </c>
       <c r="E30" s="38"/>
       <c r="F30" s="37">
@@ -40022,16 +39450,16 @@
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="37" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="B31" s="37" t="s">
-        <v>682</v>
+        <v>620</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>839</v>
+        <v>777</v>
       </c>
       <c r="E31" s="38"/>
       <c r="F31" s="37">
@@ -40040,16 +39468,16 @@
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="37" t="s">
-        <v>593</v>
+        <v>531</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>683</v>
+        <v>621</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>840</v>
+        <v>778</v>
       </c>
       <c r="E32" s="38"/>
       <c r="F32" s="37">
@@ -40058,16 +39486,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="37" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="B33" s="37" t="s">
-        <v>785</v>
+        <v>723</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="D33" s="37" t="s">
-        <v>841</v>
+        <v>779</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38">
@@ -40076,16 +39504,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="37" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>684</v>
+        <v>622</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>842</v>
+        <v>780</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38">
@@ -40094,16 +39522,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="37" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>685</v>
+        <v>623</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="D35" s="37" t="s">
-        <v>843</v>
+        <v>781</v>
       </c>
       <c r="E35" s="38"/>
       <c r="F35" s="38">
@@ -40112,16 +39540,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="37" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>686</v>
+        <v>624</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>844</v>
+        <v>782</v>
       </c>
       <c r="E36" s="38"/>
       <c r="F36" s="38">
@@ -40130,16 +39558,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="37" t="s">
-        <v>594</v>
+        <v>532</v>
       </c>
       <c r="B37" s="37" t="s">
-        <v>786</v>
+        <v>724</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="D37" s="37" t="s">
-        <v>845</v>
+        <v>783</v>
       </c>
       <c r="E37" s="38"/>
       <c r="F37" s="38">
@@ -40148,16 +39576,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="37" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>787</v>
+        <v>725</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>846</v>
+        <v>784</v>
       </c>
       <c r="E38" s="38"/>
       <c r="F38" s="38">
@@ -40166,16 +39594,16 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="37" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="B39" s="37" t="s">
-        <v>687</v>
+        <v>625</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="D39" s="37" t="s">
-        <v>847</v>
+        <v>785</v>
       </c>
       <c r="E39" s="38"/>
       <c r="F39" s="38">
@@ -40184,16 +39612,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="37" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>688</v>
+        <v>626</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>848</v>
+        <v>786</v>
       </c>
       <c r="E40" s="38"/>
       <c r="F40" s="38">
@@ -40202,16 +39630,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="37" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="B41" s="37" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>849</v>
+        <v>787</v>
       </c>
       <c r="E41" s="38"/>
       <c r="F41" s="38">
@@ -40220,16 +39648,16 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="37" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>690</v>
+        <v>628</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="D42" s="37" t="s">
-        <v>850</v>
+        <v>788</v>
       </c>
       <c r="E42" s="38"/>
       <c r="F42" s="38">
@@ -40238,16 +39666,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>788</v>
+        <v>726</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D43" s="37" t="s">
-        <v>851</v>
+        <v>789</v>
       </c>
       <c r="E43" s="38"/>
       <c r="F43" s="38">
@@ -40256,16 +39684,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>691</v>
+        <v>629</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D44" s="37" t="s">
-        <v>852</v>
+        <v>790</v>
       </c>
       <c r="E44" s="38"/>
       <c r="F44" s="37">
@@ -40274,16 +39702,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>692</v>
+        <v>630</v>
       </c>
       <c r="C45" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D45" s="37" t="s">
-        <v>853</v>
+        <v>791</v>
       </c>
       <c r="E45" s="38"/>
       <c r="F45" s="37">
@@ -40292,16 +39720,16 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>693</v>
+        <v>631</v>
       </c>
       <c r="C46" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D46" s="37" t="s">
-        <v>854</v>
+        <v>792</v>
       </c>
       <c r="E46" s="38"/>
       <c r="F46" s="38">
@@ -40310,16 +39738,16 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B47" s="37" t="s">
-        <v>859</v>
+        <v>797</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D47" s="37" t="s">
-        <v>855</v>
+        <v>793</v>
       </c>
       <c r="E47" s="38"/>
       <c r="F47" s="37">
@@ -40328,16 +39756,16 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B48" s="37" t="s">
-        <v>860</v>
+        <v>798</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D48" s="37" t="s">
-        <v>856</v>
+        <v>794</v>
       </c>
       <c r="E48" s="38"/>
       <c r="F48" s="37">
@@ -40346,16 +39774,16 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B49" s="37" t="s">
-        <v>861</v>
+        <v>799</v>
       </c>
       <c r="C49" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>857</v>
+        <v>795</v>
       </c>
       <c r="E49" s="38"/>
       <c r="F49" s="37">
@@ -40364,16 +39792,16 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="37" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="B50" s="37" t="s">
-        <v>862</v>
+        <v>800</v>
       </c>
       <c r="C50" s="37" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="D50" s="37" t="s">
-        <v>858</v>
+        <v>796</v>
       </c>
       <c r="E50" s="38"/>
       <c r="F50" s="37">
@@ -40382,16 +39810,16 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="37" t="s">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="B51" s="37" t="s">
-        <v>789</v>
+        <v>727</v>
       </c>
       <c r="C51" s="37" t="s">
-        <v>863</v>
+        <v>801</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>740</v>
+        <v>678</v>
       </c>
       <c r="E51" s="38"/>
       <c r="F51" s="37">
@@ -40400,16 +39828,16 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="37" t="s">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="B52" s="37" t="s">
-        <v>694</v>
+        <v>632</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>863</v>
+        <v>801</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>741</v>
+        <v>679</v>
       </c>
       <c r="E52" s="38"/>
       <c r="F52" s="37">
@@ -40418,16 +39846,16 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="37" t="s">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="B53" s="37" t="s">
-        <v>695</v>
+        <v>633</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>863</v>
+        <v>801</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>742</v>
+        <v>680</v>
       </c>
       <c r="E53" s="38"/>
       <c r="F53" s="37">
@@ -40436,16 +39864,16 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="37" t="s">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="B54" s="37" t="s">
-        <v>696</v>
+        <v>634</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>863</v>
+        <v>801</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>743</v>
+        <v>681</v>
       </c>
       <c r="E54" s="38"/>
       <c r="F54" s="37">
@@ -40454,16 +39882,16 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B55" s="37" t="s">
-        <v>790</v>
+        <v>728</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D55" s="37" t="s">
-        <v>864</v>
+        <v>802</v>
       </c>
       <c r="E55" s="38"/>
       <c r="F55" s="37">
@@ -40472,16 +39900,16 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B56" s="37" t="s">
-        <v>790</v>
+        <v>728</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D56" s="37" t="s">
-        <v>865</v>
+        <v>803</v>
       </c>
       <c r="E56" s="38"/>
       <c r="F56" s="37">
@@ -40490,16 +39918,16 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B57" s="37" t="s">
-        <v>697</v>
+        <v>635</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D57" s="37" t="s">
-        <v>866</v>
+        <v>804</v>
       </c>
       <c r="E57" s="38"/>
       <c r="F57" s="37">
@@ -40508,16 +39936,16 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B58" s="37" t="s">
-        <v>698</v>
+        <v>636</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D58" s="37" t="s">
-        <v>867</v>
+        <v>805</v>
       </c>
       <c r="E58" s="38"/>
       <c r="F58" s="37">
@@ -40526,16 +39954,16 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B59" s="37" t="s">
-        <v>699</v>
+        <v>637</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D59" s="37" t="s">
-        <v>868</v>
+        <v>806</v>
       </c>
       <c r="E59" s="38"/>
       <c r="F59" s="37">
@@ -40544,16 +39972,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B60" s="37" t="s">
-        <v>791</v>
+        <v>729</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D60" s="37" t="s">
-        <v>869</v>
+        <v>807</v>
       </c>
       <c r="E60" s="38"/>
       <c r="F60" s="37">
@@ -40562,16 +39990,16 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="37" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="B61" s="37" t="s">
-        <v>792</v>
+        <v>730</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>628</v>
+        <v>566</v>
       </c>
       <c r="D61" s="37" t="s">
-        <v>870</v>
+        <v>808</v>
       </c>
       <c r="E61" s="38"/>
       <c r="F61" s="37">
@@ -40580,16 +40008,16 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B62" s="37" t="s">
-        <v>793</v>
+        <v>731</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D62" s="37" t="s">
-        <v>872</v>
+        <v>810</v>
       </c>
       <c r="E62" s="38"/>
       <c r="F62" s="37">
@@ -40598,16 +40026,16 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B63" s="37" t="s">
-        <v>700</v>
+        <v>638</v>
       </c>
       <c r="C63" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>873</v>
+        <v>811</v>
       </c>
       <c r="E63" s="38"/>
       <c r="F63" s="37">
@@ -40616,16 +40044,16 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B64" s="37" t="s">
-        <v>701</v>
+        <v>639</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D64" s="37" t="s">
-        <v>874</v>
+        <v>812</v>
       </c>
       <c r="E64" s="38"/>
       <c r="F64" s="37">
@@ -40634,16 +40062,16 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B65" s="37" t="s">
-        <v>702</v>
+        <v>640</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>875</v>
+        <v>813</v>
       </c>
       <c r="E65" s="38"/>
       <c r="F65" s="37">
@@ -40652,16 +40080,16 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B66" s="37" t="s">
-        <v>703</v>
+        <v>641</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>876</v>
+        <v>814</v>
       </c>
       <c r="E66" s="38"/>
       <c r="F66" s="37">
@@ -40670,16 +40098,16 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B67" s="37" t="s">
-        <v>704</v>
+        <v>642</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D67" s="37" t="s">
-        <v>877</v>
+        <v>815</v>
       </c>
       <c r="E67" s="38"/>
       <c r="F67" s="37">
@@ -40688,16 +40116,16 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="37" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="B68" s="37" t="s">
-        <v>705</v>
+        <v>643</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>878</v>
+        <v>816</v>
       </c>
       <c r="E68" s="38"/>
       <c r="F68" s="37">
@@ -40706,16 +40134,16 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B69" s="37" t="s">
-        <v>887</v>
+        <v>825</v>
       </c>
       <c r="C69" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D69" s="37" t="s">
-        <v>879</v>
+        <v>817</v>
       </c>
       <c r="E69" s="38"/>
       <c r="F69" s="37">
@@ -40724,16 +40152,16 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B70" s="37" t="s">
-        <v>706</v>
+        <v>644</v>
       </c>
       <c r="C70" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>880</v>
+        <v>818</v>
       </c>
       <c r="E70" s="38"/>
       <c r="F70" s="37">
@@ -40742,16 +40170,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B71" s="37" t="s">
-        <v>707</v>
+        <v>645</v>
       </c>
       <c r="C71" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D71" s="37" t="s">
-        <v>881</v>
+        <v>819</v>
       </c>
       <c r="E71" s="38"/>
       <c r="F71" s="37">
@@ -40760,16 +40188,16 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="37" t="s">
+        <v>584</v>
+      </c>
+      <c r="B72" s="37" t="s">
         <v>646</v>
       </c>
-      <c r="B72" s="37" t="s">
-        <v>708</v>
-      </c>
       <c r="C72" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D72" s="37" t="s">
-        <v>882</v>
+        <v>820</v>
       </c>
       <c r="E72" s="38"/>
       <c r="F72" s="37">
@@ -40778,16 +40206,16 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B73" s="37" t="s">
-        <v>709</v>
+        <v>647</v>
       </c>
       <c r="C73" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D73" s="37" t="s">
-        <v>883</v>
+        <v>821</v>
       </c>
       <c r="E73" s="38"/>
       <c r="F73" s="37">
@@ -40796,16 +40224,16 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B74" s="37" t="s">
-        <v>710</v>
+        <v>648</v>
       </c>
       <c r="C74" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D74" s="37" t="s">
-        <v>884</v>
+        <v>822</v>
       </c>
       <c r="E74" s="38"/>
       <c r="F74" s="37">
@@ -40814,16 +40242,16 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B75" s="37" t="s">
-        <v>888</v>
+        <v>826</v>
       </c>
       <c r="C75" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D75" s="37" t="s">
-        <v>885</v>
+        <v>823</v>
       </c>
       <c r="E75" s="38"/>
       <c r="F75" s="37">
@@ -40832,16 +40260,16 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="37" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="B76" s="37" t="s">
-        <v>889</v>
+        <v>827</v>
       </c>
       <c r="C76" s="37" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D76" s="37" t="s">
-        <v>886</v>
+        <v>824</v>
       </c>
       <c r="E76" s="38"/>
       <c r="F76" s="37">
@@ -40850,16 +40278,16 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="37" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="B77" s="37" t="s">
-        <v>890</v>
+        <v>828</v>
       </c>
       <c r="C77" s="37" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="D77" s="37" t="s">
-        <v>744</v>
+        <v>682</v>
       </c>
       <c r="E77" s="38"/>
       <c r="F77" s="37">
@@ -40868,16 +40296,16 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="37" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="B78" s="37" t="s">
-        <v>711</v>
+        <v>649</v>
       </c>
       <c r="C78" s="37" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="D78" s="37" t="s">
-        <v>745</v>
+        <v>683</v>
       </c>
       <c r="E78" s="38"/>
       <c r="F78" s="37">
@@ -40886,16 +40314,16 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="37" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="B79" s="37" t="s">
-        <v>712</v>
+        <v>650</v>
       </c>
       <c r="C79" s="37" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="D79" s="37" t="s">
-        <v>803</v>
+        <v>741</v>
       </c>
       <c r="E79" s="38"/>
       <c r="F79" s="37">
@@ -40904,16 +40332,16 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="37" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="B80" s="37" t="s">
-        <v>713</v>
+        <v>651</v>
       </c>
       <c r="C80" s="37" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="D80" s="37" t="s">
-        <v>804</v>
+        <v>742</v>
       </c>
       <c r="E80" s="38"/>
       <c r="F80" s="37">
@@ -40922,16 +40350,16 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B81" s="37" t="s">
-        <v>899</v>
+        <v>837</v>
       </c>
       <c r="C81" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D81" s="37" t="s">
-        <v>898</v>
+        <v>836</v>
       </c>
       <c r="E81" s="38"/>
       <c r="F81" s="37">
@@ -40940,16 +40368,16 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B82" s="37" t="s">
-        <v>714</v>
+        <v>652</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D82" s="37" t="s">
-        <v>891</v>
+        <v>829</v>
       </c>
       <c r="E82" s="38"/>
       <c r="F82" s="37">
@@ -40958,16 +40386,16 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B83" s="37" t="s">
-        <v>715</v>
+        <v>653</v>
       </c>
       <c r="C83" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D83" s="37" t="s">
-        <v>892</v>
+        <v>830</v>
       </c>
       <c r="E83" s="38"/>
       <c r="F83" s="37">
@@ -40976,16 +40404,16 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B84" s="37" t="s">
-        <v>716</v>
+        <v>654</v>
       </c>
       <c r="C84" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D84" s="37" t="s">
-        <v>893</v>
+        <v>831</v>
       </c>
       <c r="E84" s="38"/>
       <c r="F84" s="37">
@@ -40994,16 +40422,16 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B85" s="37" t="s">
-        <v>717</v>
+        <v>655</v>
       </c>
       <c r="C85" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>894</v>
+        <v>832</v>
       </c>
       <c r="E85" s="38"/>
       <c r="F85" s="37">
@@ -41012,16 +40440,16 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B86" s="37" t="s">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="C86" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>895</v>
+        <v>833</v>
       </c>
       <c r="E86" s="38"/>
       <c r="F86" s="37">
@@ -41030,16 +40458,16 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B87" s="37" t="s">
-        <v>900</v>
+        <v>838</v>
       </c>
       <c r="C87" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D87" s="37" t="s">
-        <v>896</v>
+        <v>834</v>
       </c>
       <c r="E87" s="38"/>
       <c r="F87" s="37">
@@ -41048,16 +40476,16 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="37" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="B88" s="37" t="s">
-        <v>901</v>
+        <v>839</v>
       </c>
       <c r="C88" s="37" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="D88" s="37" t="s">
-        <v>897</v>
+        <v>835</v>
       </c>
       <c r="E88" s="38"/>
       <c r="F88" s="37">
@@ -41066,16 +40494,16 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B89" s="37" t="s">
-        <v>902</v>
+        <v>840</v>
       </c>
       <c r="C89" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D89" s="37" t="s">
-        <v>746</v>
+        <v>684</v>
       </c>
       <c r="E89" s="38"/>
       <c r="F89" s="37">
@@ -41084,16 +40512,16 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B90" s="37" t="s">
-        <v>719</v>
+        <v>657</v>
       </c>
       <c r="C90" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D90" s="37" t="s">
-        <v>747</v>
+        <v>685</v>
       </c>
       <c r="E90" s="38"/>
       <c r="F90" s="37">
@@ -41102,16 +40530,16 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B91" s="37" t="s">
-        <v>720</v>
+        <v>658</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D91" s="37" t="s">
-        <v>748</v>
+        <v>686</v>
       </c>
       <c r="E91" s="38"/>
       <c r="F91" s="37">
@@ -41120,16 +40548,16 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B92" s="37" t="s">
-        <v>721</v>
+        <v>659</v>
       </c>
       <c r="C92" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D92" s="37" t="s">
-        <v>749</v>
+        <v>687</v>
       </c>
       <c r="E92" s="38"/>
       <c r="F92" s="37">
@@ -41138,16 +40566,16 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B93" s="37" t="s">
-        <v>722</v>
+        <v>660</v>
       </c>
       <c r="C93" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D93" s="37" t="s">
-        <v>750</v>
+        <v>688</v>
       </c>
       <c r="E93" s="38"/>
       <c r="F93" s="37">
@@ -41156,16 +40584,16 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B94" s="37" t="s">
-        <v>723</v>
+        <v>661</v>
       </c>
       <c r="C94" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D94" s="37" t="s">
-        <v>751</v>
+        <v>689</v>
       </c>
       <c r="E94" s="38"/>
       <c r="F94" s="37">
@@ -41174,16 +40602,16 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B95" s="37" t="s">
-        <v>724</v>
+        <v>662</v>
       </c>
       <c r="C95" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D95" s="37" t="s">
-        <v>752</v>
+        <v>690</v>
       </c>
       <c r="E95" s="38"/>
       <c r="F95" s="37">
@@ -41192,16 +40620,16 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="37" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="B96" s="37" t="s">
-        <v>725</v>
+        <v>663</v>
       </c>
       <c r="C96" s="37" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="D96" s="37" t="s">
-        <v>753</v>
+        <v>691</v>
       </c>
       <c r="E96" s="38"/>
       <c r="F96" s="37">
@@ -41210,16 +40638,16 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B97" s="37" t="s">
-        <v>794</v>
+        <v>732</v>
       </c>
       <c r="C97" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D97" s="37" t="s">
-        <v>754</v>
+        <v>692</v>
       </c>
       <c r="E97" s="38"/>
       <c r="F97" s="37">
@@ -41228,16 +40656,16 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B98" s="37" t="s">
-        <v>726</v>
+        <v>664</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D98" s="37" t="s">
-        <v>755</v>
+        <v>693</v>
       </c>
       <c r="E98" s="38"/>
       <c r="F98" s="37">
@@ -41246,16 +40674,16 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B99" s="37" t="s">
-        <v>727</v>
+        <v>665</v>
       </c>
       <c r="C99" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D99" s="37" t="s">
-        <v>756</v>
+        <v>694</v>
       </c>
       <c r="E99" s="38"/>
       <c r="F99" s="37">
@@ -41264,16 +40692,16 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B100" s="37" t="s">
-        <v>728</v>
+        <v>666</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D100" s="37" t="s">
-        <v>757</v>
+        <v>695</v>
       </c>
       <c r="E100" s="38"/>
       <c r="F100" s="37">
@@ -41282,16 +40710,16 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B101" s="37" t="s">
-        <v>729</v>
+        <v>667</v>
       </c>
       <c r="C101" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D101" s="37" t="s">
-        <v>758</v>
+        <v>696</v>
       </c>
       <c r="E101" s="38"/>
       <c r="F101" s="37">
@@ -41300,16 +40728,16 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B102" s="37" t="s">
-        <v>730</v>
+        <v>668</v>
       </c>
       <c r="C102" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>759</v>
+        <v>697</v>
       </c>
       <c r="E102" s="38"/>
       <c r="F102" s="37">
@@ -41318,16 +40746,16 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B103" s="37" t="s">
-        <v>731</v>
+        <v>669</v>
       </c>
       <c r="C103" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D103" s="37" t="s">
-        <v>805</v>
+        <v>743</v>
       </c>
       <c r="E103" s="38"/>
       <c r="F103" s="37">
@@ -41336,16 +40764,16 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B104" s="37" t="s">
-        <v>732</v>
+        <v>670</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D104" s="37" t="s">
-        <v>760</v>
+        <v>698</v>
       </c>
       <c r="E104" s="38"/>
       <c r="F104" s="37">
@@ -41354,16 +40782,16 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="37" t="s">
-        <v>595</v>
+        <v>533</v>
       </c>
       <c r="B105" s="37" t="s">
-        <v>733</v>
+        <v>671</v>
       </c>
       <c r="C105" s="37" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="D105" s="37" t="s">
-        <v>761</v>
+        <v>699</v>
       </c>
       <c r="E105" s="38"/>
       <c r="F105" s="37">
@@ -41372,16 +40800,16 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="37" t="s">
-        <v>597</v>
+        <v>535</v>
       </c>
       <c r="B106" s="37" t="s">
-        <v>795</v>
+        <v>733</v>
       </c>
       <c r="C106" s="37" t="s">
-        <v>653</v>
+        <v>591</v>
       </c>
       <c r="D106" s="37" t="s">
-        <v>762</v>
+        <v>700</v>
       </c>
       <c r="E106" s="38"/>
       <c r="F106" s="37">
@@ -41390,16 +40818,16 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="37" t="s">
-        <v>597</v>
+        <v>535</v>
       </c>
       <c r="B107" s="37" t="s">
-        <v>796</v>
+        <v>734</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>653</v>
+        <v>591</v>
       </c>
       <c r="D107" s="37" t="s">
-        <v>763</v>
+        <v>701</v>
       </c>
       <c r="E107" s="38"/>
       <c r="F107" s="37">
@@ -41408,16 +40836,16 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="37" t="s">
-        <v>597</v>
+        <v>535</v>
       </c>
       <c r="B108" s="37" t="s">
-        <v>797</v>
+        <v>735</v>
       </c>
       <c r="C108" s="37" t="s">
-        <v>653</v>
+        <v>591</v>
       </c>
       <c r="D108" s="37" t="s">
-        <v>764</v>
+        <v>702</v>
       </c>
       <c r="E108" s="38"/>
       <c r="F108" s="37">
@@ -41426,16 +40854,16 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B109" s="37" t="s">
-        <v>798</v>
+        <v>736</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D109" s="37" t="s">
-        <v>765</v>
+        <v>703</v>
       </c>
       <c r="E109" s="38"/>
       <c r="F109" s="37">
@@ -41444,16 +40872,16 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B110" s="37" t="s">
-        <v>903</v>
+        <v>841</v>
       </c>
       <c r="C110" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D110" s="37" t="s">
-        <v>766</v>
+        <v>704</v>
       </c>
       <c r="E110" s="38"/>
       <c r="F110" s="37">
@@ -41462,16 +40890,16 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B111" s="37" t="s">
-        <v>904</v>
+        <v>842</v>
       </c>
       <c r="C111" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D111" s="37" t="s">
-        <v>767</v>
+        <v>705</v>
       </c>
       <c r="E111" s="38"/>
       <c r="F111" s="37">
@@ -41480,16 +40908,16 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B112" s="37" t="s">
-        <v>905</v>
+        <v>843</v>
       </c>
       <c r="C112" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D112" s="37" t="s">
-        <v>768</v>
+        <v>706</v>
       </c>
       <c r="E112" s="38"/>
       <c r="F112" s="37">
@@ -41498,16 +40926,16 @@
     </row>
     <row r="113" spans="1:6" ht="30">
       <c r="A113" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B113" s="37" t="s">
-        <v>906</v>
+        <v>844</v>
       </c>
       <c r="C113" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D113" s="37" t="s">
-        <v>769</v>
+        <v>707</v>
       </c>
       <c r="E113" s="38"/>
       <c r="F113" s="37">
@@ -41516,16 +40944,16 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B114" s="37" t="s">
-        <v>907</v>
+        <v>845</v>
       </c>
       <c r="C114" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D114" s="37" t="s">
-        <v>770</v>
+        <v>708</v>
       </c>
       <c r="E114" s="38"/>
       <c r="F114" s="37">
@@ -41534,16 +40962,16 @@
     </row>
     <row r="115" spans="1:6" ht="30">
       <c r="A115" s="37" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="B115" s="37" t="s">
-        <v>908</v>
+        <v>846</v>
       </c>
       <c r="C115" s="37" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="D115" s="37" t="s">
-        <v>771</v>
+        <v>709</v>
       </c>
       <c r="E115" s="38"/>
       <c r="F115" s="37">
@@ -41552,16 +40980,16 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="37" t="s">
-        <v>655</v>
+        <v>593</v>
       </c>
       <c r="B116" s="37" t="s">
-        <v>799</v>
+        <v>737</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>656</v>
+        <v>594</v>
       </c>
       <c r="D116" s="37" t="s">
-        <v>772</v>
+        <v>710</v>
       </c>
       <c r="E116" s="38"/>
       <c r="F116" s="37">
@@ -41570,16 +40998,16 @@
     </row>
     <row r="117" spans="1:6" ht="30">
       <c r="A117" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B117" s="37" t="s">
-        <v>800</v>
+        <v>738</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D117" s="37" t="s">
-        <v>773</v>
+        <v>711</v>
       </c>
       <c r="E117" s="38"/>
       <c r="F117" s="37">
@@ -41588,16 +41016,16 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B118" s="37" t="s">
-        <v>734</v>
+        <v>672</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D118" s="37" t="s">
-        <v>774</v>
+        <v>712</v>
       </c>
       <c r="E118" s="38"/>
       <c r="F118" s="37">
@@ -41606,16 +41034,16 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B119" s="37" t="s">
-        <v>735</v>
+        <v>673</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D119" s="37" t="s">
-        <v>775</v>
+        <v>713</v>
       </c>
       <c r="E119" s="38"/>
       <c r="F119" s="37">
@@ -41624,16 +41052,16 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B120" s="37" t="s">
-        <v>736</v>
+        <v>674</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D120" s="37" t="s">
-        <v>776</v>
+        <v>714</v>
       </c>
       <c r="E120" s="38"/>
       <c r="F120" s="37">
@@ -41642,16 +41070,16 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B121" s="37" t="s">
-        <v>737</v>
+        <v>675</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D121" s="37" t="s">
-        <v>806</v>
+        <v>744</v>
       </c>
       <c r="E121" s="38"/>
       <c r="F121" s="37">
@@ -41660,16 +41088,16 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B122" s="37" t="s">
-        <v>738</v>
+        <v>676</v>
       </c>
       <c r="C122" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D122" s="37" t="s">
-        <v>807</v>
+        <v>745</v>
       </c>
       <c r="E122" s="38"/>
       <c r="F122" s="37">
@@ -41678,16 +41106,16 @@
     </row>
     <row r="123" spans="1:6" ht="30">
       <c r="A123" s="37" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="B123" s="37" t="s">
-        <v>739</v>
+        <v>677</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="D123" s="37" t="s">
-        <v>777</v>
+        <v>715</v>
       </c>
       <c r="E123" s="38"/>
       <c r="F123" s="37">
@@ -41696,16 +41124,16 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="37" t="s">
-        <v>801</v>
+        <v>739</v>
       </c>
       <c r="B124" s="37" t="s">
-        <v>802</v>
+        <v>740</v>
       </c>
       <c r="C124" s="37" t="s">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="D124" s="37" t="s">
-        <v>778</v>
+        <v>716</v>
       </c>
       <c r="E124" s="38"/>
       <c r="F124" s="37">
@@ -41714,16 +41142,16 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="37" t="s">
-        <v>801</v>
+        <v>739</v>
       </c>
       <c r="B125" s="37" t="s">
-        <v>909</v>
+        <v>847</v>
       </c>
       <c r="C125" s="37" t="s">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="D125" s="37" t="s">
-        <v>779</v>
+        <v>717</v>
       </c>
       <c r="E125" s="38"/>
       <c r="F125" s="37">
@@ -41732,16 +41160,16 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="37" t="s">
-        <v>801</v>
+        <v>739</v>
       </c>
       <c r="B126" s="37" t="s">
-        <v>910</v>
+        <v>848</v>
       </c>
       <c r="C126" s="37" t="s">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="D126" s="37" t="s">
-        <v>780</v>
+        <v>718</v>
       </c>
       <c r="E126" s="38"/>
       <c r="F126" s="37">
@@ -41778,37 +41206,37 @@
   <sheetData>
     <row r="1" spans="1:11" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
-        <v>605</v>
+        <v>543</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>578</v>
+        <v>516</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>607</v>
+        <v>545</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>608</v>
+        <v>546</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>609</v>
+        <v>547</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>610</v>
+        <v>548</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>611</v>
+        <v>549</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>612</v>
+        <v>550</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>613</v>
+        <v>551</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="60">
@@ -41816,13 +41244,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>584</v>
+        <v>522</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="D2" s="37" t="s">
-        <v>926</v>
+        <v>864</v>
       </c>
       <c r="E2" s="37">
         <v>1</v>
@@ -41837,7 +41265,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>928</v>
+        <v>866</v>
       </c>
       <c r="J2" s="37"/>
       <c r="K2" s="37">
@@ -41867,37 +41295,37 @@
   <sheetData>
     <row r="1" spans="1:12" s="26" customFormat="1" ht="15">
       <c r="A1" s="39" t="s">
-        <v>924</v>
+        <v>862</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>614</v>
+        <v>552</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>578</v>
+        <v>516</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>580</v>
+        <v>518</v>
       </c>
       <c r="E1" s="39" t="s">
-        <v>579</v>
+        <v>517</v>
       </c>
       <c r="F1" s="39" t="s">
-        <v>923</v>
+        <v>861</v>
       </c>
       <c r="G1" s="39" t="s">
-        <v>615</v>
+        <v>553</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="I1" s="39" t="s">
-        <v>616</v>
+        <v>554</v>
       </c>
       <c r="J1" s="39" t="s">
-        <v>617</v>
+        <v>555</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>618</v>
+        <v>556</v>
       </c>
       <c r="L1" s="17"/>
     </row>
@@ -41906,7 +41334,7 @@
         <v>2507238</v>
       </c>
       <c r="B2" t="s">
-        <v>927</v>
+        <v>865</v>
       </c>
       <c r="K2" s="33"/>
     </row>
@@ -41918,17 +41346,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16bed903-0179-4e60-92c1-b9da8d5f7bbf">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010064913C44E1F1CB4CB693756E7EC2D392" ma:contentTypeVersion="12" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ca67994ffd5ed131a557285f1e41756c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="16bed903-0179-4e60-92c1-b9da8d5f7bbf" xmlns:ns3="2b5b1759-8281-4e33-bc6b-4f502641d3cc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa37a9092383deea460b40ff1715ceb" ns2:_="" ns3:_="">
     <xsd:import namespace="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
@@ -42129,6 +41546,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="16bed903-0179-4e60-92c1-b9da8d5f7bbf">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -42139,17 +41567,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
-    <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6479191D-8696-400D-B5CD-A3DAFAE30633}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -42168,6 +41585,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2b5b1759-8281-4e33-bc6b-4f502641d3cc"/>
+    <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
   <ds:schemaRefs>

--- a/DATA/知識庫實驗品.xlsx
+++ b/DATA/知識庫實驗品.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E3FAC5F-80CD-4B84-91D4-B2D8A2083BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746664E3-6A19-46BC-8B4D-01CCD8CA60C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="884">
   <si>
     <t>序號</t>
   </si>
@@ -3026,6 +3026,9 @@
   <si>
     <t>林珈青</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新人</t>
   </si>
 </sst>
 </file>
@@ -36926,6 +36929,9 @@
       <c r="B2" s="32" t="s">
         <v>882</v>
       </c>
+      <c r="E2" s="32" t="s">
+        <v>883</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -41547,6 +41553,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="2b5b1759-8281-4e33-bc6b-4f502641d3cc" xsi:nil="true"/>
@@ -41555,15 +41570,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -41586,6 +41592,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02504D25-C599-4D34-8B55-9105437235CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -41594,12 +41608,4 @@
     <ds:schemaRef ds:uri="16bed903-0179-4e60-92c1-b9da8d5f7bbf"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B469A2E-F777-4C2F-9A47-C6A468152A6E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>